--- a/03. CMH120 OFCI Log REV2.0.xlsx
+++ b/03. CMH120 OFCI Log REV2.0.xlsx
@@ -2066,7 +2066,7 @@
       <c r="P3" s="17"/>
       <c r="Q3" s="15"/>
     </row>
-    <row r="4" hidden="false" outlineLevel="1">
+    <row r="4" hidden="true" outlineLevel="1">
       <c r="A4" s="21"/>
       <c r="B4" s="5"/>
       <c r="C4" s="7"/>
@@ -2085,7 +2085,7 @@
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
     </row>
-    <row r="5" hidden="false" outlineLevel="1">
+    <row r="5" hidden="true" outlineLevel="1">
       <c r="A5" t="s" s="23">
         <v>19</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="6" hidden="false" outlineLevel="2">
+    <row r="6" hidden="true" outlineLevel="2">
       <c r="A6" t="s" s="35">
         <v>21</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="7" hidden="false" outlineLevel="2">
+    <row r="7" hidden="true" outlineLevel="2">
       <c r="A7" t="s" s="35">
         <v>21</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="8" hidden="false" outlineLevel="2">
+    <row r="8" hidden="true" outlineLevel="2">
       <c r="A8" t="s" s="35">
         <v>21</v>
       </c>
@@ -2247,7 +2247,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="9" hidden="false" outlineLevel="2">
+    <row r="9" hidden="true" outlineLevel="2">
       <c r="A9" t="s" s="35">
         <v>21</v>
       </c>
@@ -2284,7 +2284,7 @@
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
     </row>
-    <row r="10" hidden="false" outlineLevel="2">
+    <row r="10" hidden="true" outlineLevel="2">
       <c r="A10" t="s" s="35">
         <v>21</v>
       </c>
@@ -2321,7 +2321,7 @@
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
     </row>
-    <row r="11" hidden="false" outlineLevel="2">
+    <row r="11" hidden="true" outlineLevel="2">
       <c r="A11" t="s" s="35">
         <v>32</v>
       </c>
@@ -2366,7 +2366,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="12" hidden="false" outlineLevel="2">
+    <row r="12" hidden="true" outlineLevel="2">
       <c r="A12" t="s" s="35">
         <v>34</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="13" hidden="false" outlineLevel="1">
+    <row r="13" hidden="true" outlineLevel="1">
       <c r="A13" t="s" s="23">
         <v>35</v>
       </c>
@@ -2438,7 +2438,7 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="14" hidden="false" outlineLevel="2">
+    <row r="14" hidden="true" outlineLevel="2">
       <c r="A14" t="s" s="35">
         <v>36</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="15" hidden="false" outlineLevel="2">
+    <row r="15" hidden="true" outlineLevel="2">
       <c r="A15" t="s" s="35">
         <v>36</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="16" hidden="false" outlineLevel="2">
+    <row r="16" hidden="true" outlineLevel="2">
       <c r="A16" t="s" s="35">
         <v>40</v>
       </c>
@@ -2573,7 +2573,7 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="17" hidden="false" outlineLevel="2">
+    <row r="17" hidden="true" outlineLevel="2">
       <c r="A17" t="s" s="35">
         <v>41</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="18" hidden="false" outlineLevel="1">
+    <row r="18" hidden="true" outlineLevel="1">
       <c r="A18" t="s" s="23">
         <v>42</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="19" hidden="false" outlineLevel="2">
+    <row r="19" hidden="true" outlineLevel="2">
       <c r="A19" t="s" s="35">
         <v>43</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="20" hidden="false" outlineLevel="2">
+    <row r="20" hidden="true" outlineLevel="2">
       <c r="A20" t="s" s="35">
         <v>43</v>
       </c>
@@ -2735,7 +2735,7 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="21" hidden="false" outlineLevel="2">
+    <row r="21" hidden="true" outlineLevel="2">
       <c r="A21" t="s" s="35">
         <v>47</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="22" hidden="false" outlineLevel="2">
+    <row r="22" hidden="true" outlineLevel="2">
       <c r="A22" t="s" s="35">
         <v>48</v>
       </c>
@@ -2825,7 +2825,7 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="23" hidden="false" outlineLevel="1">
+    <row r="23" hidden="true" outlineLevel="1">
       <c r="A23" t="s" s="23">
         <v>49</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="24" hidden="false" outlineLevel="2">
+    <row r="24" hidden="true" outlineLevel="2">
       <c r="A24" t="s" s="35">
         <v>50</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="25" hidden="false" outlineLevel="2">
+    <row r="25" hidden="true" outlineLevel="2">
       <c r="A25" t="s" s="35">
         <v>50</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="26" hidden="false" outlineLevel="2">
+    <row r="26" hidden="true" outlineLevel="2">
       <c r="A26" t="s" s="35">
         <v>54</v>
       </c>
@@ -2987,7 +2987,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="27" hidden="false" outlineLevel="2">
+    <row r="27" hidden="true" outlineLevel="2">
       <c r="A27" t="s" s="35">
         <v>55</v>
       </c>
@@ -3032,7 +3032,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="28" hidden="false" outlineLevel="1">
+    <row r="28" hidden="true" outlineLevel="1">
       <c r="A28" t="s" s="23">
         <v>56</v>
       </c>
@@ -3057,7 +3057,7 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="29" hidden="false" outlineLevel="2">
+    <row r="29" hidden="true" outlineLevel="2">
       <c r="A29" t="s" s="35">
         <v>57</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="30" hidden="false" outlineLevel="2">
+    <row r="30" hidden="true" outlineLevel="2">
       <c r="A30" t="s" s="35">
         <v>57</v>
       </c>
@@ -3147,7 +3147,7 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="31" hidden="false" outlineLevel="2">
+    <row r="31" hidden="true" outlineLevel="2">
       <c r="A31" t="s" s="35">
         <v>61</v>
       </c>
@@ -3192,7 +3192,7 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="32" hidden="false" outlineLevel="2">
+    <row r="32" hidden="true" outlineLevel="2">
       <c r="A32" t="s" s="35">
         <v>62</v>
       </c>
@@ -3237,7 +3237,7 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="33" hidden="false" outlineLevel="1">
+    <row r="33" hidden="true" outlineLevel="1">
       <c r="A33" t="s" s="23">
         <v>63</v>
       </c>
@@ -3262,7 +3262,7 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="34" hidden="false" outlineLevel="2">
+    <row r="34" hidden="true" outlineLevel="2">
       <c r="A34" t="s" s="35">
         <v>64</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="35" hidden="false" outlineLevel="2">
+    <row r="35" hidden="true" outlineLevel="2">
       <c r="A35" t="s" s="35">
         <v>64</v>
       </c>
@@ -3352,7 +3352,7 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="36" hidden="false" outlineLevel="2">
+    <row r="36" hidden="true" outlineLevel="2">
       <c r="A36" t="s" s="35">
         <v>68</v>
       </c>
@@ -3397,7 +3397,7 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="37" hidden="false" outlineLevel="2">
+    <row r="37" hidden="true" outlineLevel="2">
       <c r="A37" t="s" s="35">
         <v>69</v>
       </c>
@@ -3442,7 +3442,7 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="38" hidden="false" outlineLevel="1">
+    <row r="38" hidden="true" outlineLevel="1">
       <c r="A38" t="s" s="23">
         <v>70</v>
       </c>
@@ -3467,7 +3467,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="39" hidden="false" outlineLevel="2">
+    <row r="39" hidden="true" outlineLevel="2">
       <c r="A39" t="s" s="35">
         <v>71</v>
       </c>
@@ -3512,7 +3512,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="40" hidden="false" outlineLevel="2">
+    <row r="40" hidden="true" outlineLevel="2">
       <c r="A40" t="s" s="35">
         <v>71</v>
       </c>
@@ -3557,7 +3557,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="41" hidden="false" outlineLevel="2">
+    <row r="41" hidden="true" outlineLevel="2">
       <c r="A41" t="s" s="35">
         <v>71</v>
       </c>
@@ -3602,7 +3602,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="42" hidden="false" outlineLevel="2">
+    <row r="42" hidden="true" outlineLevel="2">
       <c r="A42" t="s" s="35">
         <v>75</v>
       </c>
@@ -3647,7 +3647,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="43" hidden="false" outlineLevel="2">
+    <row r="43" hidden="true" outlineLevel="2">
       <c r="A43" t="s" s="35">
         <v>76</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="44" hidden="false" outlineLevel="1">
+    <row r="44" hidden="true" outlineLevel="1">
       <c r="A44" t="s" s="23">
         <v>77</v>
       </c>
@@ -3717,7 +3717,7 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="45" hidden="false" outlineLevel="2">
+    <row r="45" hidden="true" outlineLevel="2">
       <c r="A45" t="s" s="35">
         <v>78</v>
       </c>
@@ -3762,7 +3762,7 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="46" hidden="false" outlineLevel="2">
+    <row r="46" hidden="true" outlineLevel="2">
       <c r="A46" t="s" s="35">
         <v>78</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="47" hidden="false" outlineLevel="2">
+    <row r="47" hidden="true" outlineLevel="2">
       <c r="A47" t="s" s="35">
         <v>82</v>
       </c>
@@ -3852,7 +3852,7 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="48" hidden="false" outlineLevel="2">
+    <row r="48" hidden="true" outlineLevel="2">
       <c r="A48" t="s" s="35">
         <v>83</v>
       </c>
@@ -3897,7 +3897,7 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="49" hidden="false" outlineLevel="1">
+    <row r="49" hidden="true" outlineLevel="1">
       <c r="A49" t="s" s="23">
         <v>84</v>
       </c>
@@ -3922,7 +3922,7 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="50" hidden="false" outlineLevel="2">
+    <row r="50" hidden="true" outlineLevel="2">
       <c r="A50" t="s" s="35">
         <v>85</v>
       </c>
@@ -3967,7 +3967,7 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="51" hidden="false" outlineLevel="2">
+    <row r="51" hidden="true" outlineLevel="2">
       <c r="A51" t="s" s="35">
         <v>85</v>
       </c>
@@ -4012,7 +4012,7 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="52" hidden="false" outlineLevel="2">
+    <row r="52" hidden="true" outlineLevel="2">
       <c r="A52" t="s" s="35">
         <v>87</v>
       </c>
@@ -4057,7 +4057,7 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="53" hidden="false" outlineLevel="2">
+    <row r="53" hidden="true" outlineLevel="2">
       <c r="A53" t="s" s="35">
         <v>88</v>
       </c>
@@ -4102,7 +4102,7 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="54" hidden="false" outlineLevel="1">
+    <row r="54" hidden="true" outlineLevel="1">
       <c r="A54" t="s" s="23">
         <v>89</v>
       </c>
@@ -4127,7 +4127,7 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="55" hidden="false" outlineLevel="2">
+    <row r="55" hidden="true" outlineLevel="2">
       <c r="A55" t="s" s="35">
         <v>90</v>
       </c>
@@ -4172,7 +4172,7 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="56" hidden="false" outlineLevel="2">
+    <row r="56" hidden="true" outlineLevel="2">
       <c r="A56" t="s" s="35">
         <v>90</v>
       </c>
@@ -4217,7 +4217,7 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="57" hidden="false" outlineLevel="2">
+    <row r="57" hidden="true" outlineLevel="2">
       <c r="A57" t="s" s="35">
         <v>94</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="58" hidden="false" outlineLevel="2">
+    <row r="58" hidden="true" outlineLevel="2">
       <c r="A58" t="s" s="35">
         <v>95</v>
       </c>
@@ -4307,7 +4307,7 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="59" hidden="false" outlineLevel="1">
+    <row r="59" hidden="true" outlineLevel="1">
       <c r="A59" t="s" s="23">
         <v>96</v>
       </c>
@@ -4332,7 +4332,7 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="60" hidden="false" outlineLevel="2">
+    <row r="60" hidden="true" outlineLevel="2">
       <c r="A60" t="s" s="35">
         <v>97</v>
       </c>
@@ -4377,7 +4377,7 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="61" hidden="false" outlineLevel="2">
+    <row r="61" hidden="true" outlineLevel="2">
       <c r="A61" t="s" s="35">
         <v>97</v>
       </c>
@@ -4422,7 +4422,7 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="62" hidden="false" outlineLevel="2">
+    <row r="62" hidden="true" outlineLevel="2">
       <c r="A62" t="s" s="35">
         <v>101</v>
       </c>
@@ -4467,7 +4467,7 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="63" hidden="false" outlineLevel="2">
+    <row r="63" hidden="true" outlineLevel="2">
       <c r="A63" t="s" s="35">
         <v>102</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="64" hidden="false" outlineLevel="1">
+    <row r="64" hidden="true" outlineLevel="1">
       <c r="A64" t="s" s="23">
         <v>103</v>
       </c>
@@ -4537,7 +4537,7 @@
         <v>46412.0</v>
       </c>
     </row>
-    <row r="65" hidden="false" outlineLevel="2">
+    <row r="65" hidden="true" outlineLevel="2">
       <c r="A65" t="s" s="35">
         <v>104</v>
       </c>
@@ -4582,7 +4582,7 @@
         <v>46412.0</v>
       </c>
     </row>
-    <row r="66" hidden="false" outlineLevel="2">
+    <row r="66" hidden="true" outlineLevel="2">
       <c r="A66" t="s" s="35">
         <v>104</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>46412.0</v>
       </c>
     </row>
-    <row r="67" hidden="false" outlineLevel="2">
+    <row r="67" hidden="true" outlineLevel="2">
       <c r="A67" t="s" s="35">
         <v>108</v>
       </c>
@@ -4672,7 +4672,7 @@
         <v>46412.0</v>
       </c>
     </row>
-    <row r="68" hidden="false" outlineLevel="2">
+    <row r="68" hidden="true" outlineLevel="2">
       <c r="A68" t="s" s="35">
         <v>109</v>
       </c>
@@ -4776,7 +4776,7 @@
       <c r="P71" s="15"/>
       <c r="Q71" s="15"/>
     </row>
-    <row r="72" hidden="false" outlineLevel="1">
+    <row r="72" hidden="true" outlineLevel="1">
       <c r="A72" t="s" s="45">
         <v>111</v>
       </c>
@@ -4821,7 +4821,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="73" hidden="false" outlineLevel="1">
+    <row r="73" hidden="true" outlineLevel="1">
       <c r="A73" t="s" s="23">
         <v>111</v>
       </c>
@@ -8270,7 +8270,7 @@
       <c r="P163" s="15"/>
       <c r="Q163" s="15"/>
     </row>
-    <row r="164" hidden="false" outlineLevel="1">
+    <row r="164" hidden="true" outlineLevel="1">
       <c r="A164" s="21"/>
       <c r="B164" s="5"/>
       <c r="C164" s="7"/>
@@ -8291,7 +8291,7 @@
       <c r="P164" s="5"/>
       <c r="Q164" s="5"/>
     </row>
-    <row r="165" hidden="false" outlineLevel="1">
+    <row r="165" hidden="true" outlineLevel="1">
       <c r="A165" t="s" s="21">
         <v>201</v>
       </c>
@@ -8336,7 +8336,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="166" hidden="false" outlineLevel="1">
+    <row r="166" hidden="true" outlineLevel="1">
       <c r="A166" t="s" s="23">
         <v>205</v>
       </c>
@@ -8381,7 +8381,7 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="167" hidden="false" outlineLevel="1">
+    <row r="167" hidden="true" outlineLevel="1">
       <c r="A167" t="s" s="21">
         <v>206</v>
       </c>
@@ -8426,7 +8426,7 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="168" hidden="false" outlineLevel="1">
+    <row r="168" hidden="true" outlineLevel="1">
       <c r="A168" t="s" s="23">
         <v>207</v>
       </c>
@@ -8471,7 +8471,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="169" hidden="false" outlineLevel="1">
+    <row r="169" hidden="true" outlineLevel="1">
       <c r="A169" t="s" s="21">
         <v>208</v>
       </c>
@@ -8516,7 +8516,7 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="170" hidden="false" outlineLevel="1">
+    <row r="170" hidden="true" outlineLevel="1">
       <c r="A170" t="s" s="23">
         <v>209</v>
       </c>
@@ -8561,7 +8561,7 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="171" hidden="false" outlineLevel="1">
+    <row r="171" hidden="true" outlineLevel="1">
       <c r="A171" t="s" s="21">
         <v>210</v>
       </c>
@@ -8606,7 +8606,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="172" hidden="false" outlineLevel="1">
+    <row r="172" hidden="true" outlineLevel="1">
       <c r="A172" t="s" s="23">
         <v>211</v>
       </c>
@@ -8651,7 +8651,7 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="173" hidden="false" outlineLevel="1">
+    <row r="173" hidden="true" outlineLevel="1">
       <c r="A173" t="s" s="21">
         <v>212</v>
       </c>
@@ -8696,7 +8696,7 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="174" hidden="false" outlineLevel="1">
+    <row r="174" hidden="true" outlineLevel="1">
       <c r="A174" t="s" s="23">
         <v>213</v>
       </c>
@@ -8741,7 +8741,7 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="175" hidden="false" outlineLevel="1">
+    <row r="175" hidden="true" outlineLevel="1">
       <c r="A175" t="s" s="21">
         <v>214</v>
       </c>
@@ -8786,7 +8786,7 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="176" hidden="false" outlineLevel="1">
+    <row r="176" hidden="true" outlineLevel="1">
       <c r="A176" t="s" s="23">
         <v>215</v>
       </c>
@@ -10089,7 +10089,7 @@
       <c r="P210" s="81"/>
       <c r="Q210" s="81"/>
     </row>
-    <row r="211" hidden="false" outlineLevel="1">
+    <row r="211" hidden="true" outlineLevel="1">
       <c r="A211" s="21"/>
       <c r="B211" s="5"/>
       <c r="C211" s="7"/>
@@ -10108,7 +10108,7 @@
       <c r="P211" s="5"/>
       <c r="Q211" s="5"/>
     </row>
-    <row r="212" hidden="false" outlineLevel="1">
+    <row r="212" hidden="true" outlineLevel="1">
       <c r="A212" t="s" s="21">
         <v>251</v>
       </c>
@@ -10151,7 +10151,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="213" hidden="false" outlineLevel="1">
+    <row r="213" hidden="true" outlineLevel="1">
       <c r="A213" t="s" s="23">
         <v>255</v>
       </c>
@@ -10194,7 +10194,7 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="214" hidden="false" outlineLevel="1">
+    <row r="214" hidden="true" outlineLevel="1">
       <c r="A214" t="s" s="21">
         <v>258</v>
       </c>
@@ -10237,7 +10237,7 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="215" hidden="false" outlineLevel="1">
+    <row r="215" hidden="true" outlineLevel="1">
       <c r="A215" t="s" s="23">
         <v>259</v>
       </c>
@@ -10280,7 +10280,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="216" hidden="false" outlineLevel="1">
+    <row r="216" hidden="true" outlineLevel="1">
       <c r="A216" t="s" s="21">
         <v>261</v>
       </c>
@@ -10323,7 +10323,7 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="217" hidden="false" outlineLevel="1">
+    <row r="217" hidden="true" outlineLevel="1">
       <c r="A217" t="s" s="23">
         <v>263</v>
       </c>
@@ -10366,7 +10366,7 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="218" hidden="false" outlineLevel="1">
+    <row r="218" hidden="true" outlineLevel="1">
       <c r="A218" t="s" s="21">
         <v>265</v>
       </c>
@@ -10409,7 +10409,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="219" hidden="false" outlineLevel="1">
+    <row r="219" hidden="true" outlineLevel="1">
       <c r="A219" t="s" s="23">
         <v>267</v>
       </c>
@@ -10452,7 +10452,7 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="220" hidden="false" outlineLevel="1">
+    <row r="220" hidden="true" outlineLevel="1">
       <c r="A220" t="s" s="21">
         <v>269</v>
       </c>
@@ -10495,7 +10495,7 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="221" hidden="false" outlineLevel="1">
+    <row r="221" hidden="true" outlineLevel="1">
       <c r="A221" t="s" s="23">
         <v>271</v>
       </c>
@@ -10538,7 +10538,7 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="222" hidden="false" outlineLevel="1">
+    <row r="222" hidden="true" outlineLevel="1">
       <c r="A222" t="s" s="21">
         <v>273</v>
       </c>
@@ -10581,7 +10581,7 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="223" hidden="false" outlineLevel="1">
+    <row r="223" hidden="true" outlineLevel="1">
       <c r="A223" t="s" s="23">
         <v>275</v>
       </c>
@@ -10664,7 +10664,7 @@
       <c r="P225" s="81"/>
       <c r="Q225" s="81"/>
     </row>
-    <row r="226" hidden="false" outlineLevel="1">
+    <row r="226" hidden="true" outlineLevel="1">
       <c r="A226" s="21"/>
       <c r="B226" s="5"/>
       <c r="C226" s="7"/>
@@ -10683,7 +10683,7 @@
       <c r="P226" s="5"/>
       <c r="Q226" s="5"/>
     </row>
-    <row r="227" hidden="false" outlineLevel="1">
+    <row r="227" hidden="true" outlineLevel="1">
       <c r="A227" t="s" s="23">
         <v>19</v>
       </c>
@@ -10712,7 +10712,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="228" hidden="false" outlineLevel="2">
+    <row r="228" hidden="true" outlineLevel="2">
       <c r="A228" t="s" s="35">
         <v>278</v>
       </c>
@@ -10753,7 +10753,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="229" hidden="false" outlineLevel="2">
+    <row r="229" hidden="true" outlineLevel="2">
       <c r="A229" t="s" s="35">
         <v>278</v>
       </c>
@@ -10794,7 +10794,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="230" hidden="false" outlineLevel="2">
+    <row r="230" hidden="true" outlineLevel="2">
       <c r="A230" t="s" s="35">
         <v>278</v>
       </c>
@@ -10835,7 +10835,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="231" hidden="false" outlineLevel="2">
+    <row r="231" hidden="true" outlineLevel="2">
       <c r="A231" t="s" s="35">
         <v>278</v>
       </c>
@@ -10876,7 +10876,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="232" hidden="false" outlineLevel="2">
+    <row r="232" hidden="true" outlineLevel="2">
       <c r="A232" t="s" s="35">
         <v>278</v>
       </c>
@@ -10917,7 +10917,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="233" hidden="false" outlineLevel="1">
+    <row r="233" hidden="true" outlineLevel="1">
       <c r="A233" t="s" s="23">
         <v>35</v>
       </c>
@@ -10944,7 +10944,7 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="234" hidden="false" outlineLevel="2">
+    <row r="234" hidden="true" outlineLevel="2">
       <c r="A234" t="s" s="35">
         <v>286</v>
       </c>
@@ -10985,7 +10985,7 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="235" hidden="false" outlineLevel="2">
+    <row r="235" hidden="true" outlineLevel="2">
       <c r="A235" t="s" s="35">
         <v>286</v>
       </c>
@@ -11026,7 +11026,7 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="236" hidden="false" outlineLevel="2">
+    <row r="236" hidden="true" outlineLevel="2">
       <c r="A236" t="s" s="35">
         <v>286</v>
       </c>
@@ -11067,7 +11067,7 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="237" hidden="false" outlineLevel="2">
+    <row r="237" hidden="true" outlineLevel="2">
       <c r="A237" t="s" s="35">
         <v>286</v>
       </c>
@@ -11108,7 +11108,7 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="238" hidden="false" outlineLevel="2">
+    <row r="238" hidden="true" outlineLevel="2">
       <c r="A238" t="s" s="35">
         <v>286</v>
       </c>
@@ -11149,7 +11149,7 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="239" hidden="false" outlineLevel="1">
+    <row r="239" hidden="true" outlineLevel="1">
       <c r="A239" t="s" s="23">
         <v>42</v>
       </c>
@@ -11176,7 +11176,7 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="240" hidden="false" outlineLevel="2">
+    <row r="240" hidden="true" outlineLevel="2">
       <c r="A240" t="s" s="35">
         <v>287</v>
       </c>
@@ -11217,7 +11217,7 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="241" hidden="false" outlineLevel="2">
+    <row r="241" hidden="true" outlineLevel="2">
       <c r="A241" t="s" s="35">
         <v>287</v>
       </c>
@@ -11258,7 +11258,7 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="242" hidden="false" outlineLevel="2">
+    <row r="242" hidden="true" outlineLevel="2">
       <c r="A242" t="s" s="35">
         <v>287</v>
       </c>
@@ -11299,7 +11299,7 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="243" hidden="false" outlineLevel="2">
+    <row r="243" hidden="true" outlineLevel="2">
       <c r="A243" t="s" s="35">
         <v>287</v>
       </c>
@@ -11340,7 +11340,7 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="244" hidden="false" outlineLevel="2">
+    <row r="244" hidden="true" outlineLevel="2">
       <c r="A244" t="s" s="35">
         <v>287</v>
       </c>
@@ -11381,7 +11381,7 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="245" hidden="false" outlineLevel="1">
+    <row r="245" hidden="true" outlineLevel="1">
       <c r="A245" t="s" s="23">
         <v>49</v>
       </c>
@@ -11408,7 +11408,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="246" hidden="false" outlineLevel="2">
+    <row r="246" hidden="true" outlineLevel="2">
       <c r="A246" t="s" s="35">
         <v>288</v>
       </c>
@@ -11449,7 +11449,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="247" hidden="false" outlineLevel="2">
+    <row r="247" hidden="true" outlineLevel="2">
       <c r="A247" t="s" s="35">
         <v>288</v>
       </c>
@@ -11490,7 +11490,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="248" hidden="false" outlineLevel="2">
+    <row r="248" hidden="true" outlineLevel="2">
       <c r="A248" t="s" s="35">
         <v>288</v>
       </c>
@@ -11531,7 +11531,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="249" hidden="false" outlineLevel="2">
+    <row r="249" hidden="true" outlineLevel="2">
       <c r="A249" t="s" s="35">
         <v>288</v>
       </c>
@@ -11572,7 +11572,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="250" hidden="false" outlineLevel="2">
+    <row r="250" hidden="true" outlineLevel="2">
       <c r="A250" t="s" s="35">
         <v>288</v>
       </c>
@@ -11613,7 +11613,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="251" hidden="false" outlineLevel="1">
+    <row r="251" hidden="true" outlineLevel="1">
       <c r="A251" t="s" s="23">
         <v>56</v>
       </c>
@@ -11640,7 +11640,7 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="252" hidden="false" outlineLevel="2">
+    <row r="252" hidden="true" outlineLevel="2">
       <c r="A252" t="s" s="35">
         <v>289</v>
       </c>
@@ -11681,7 +11681,7 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="253" hidden="false" outlineLevel="2">
+    <row r="253" hidden="true" outlineLevel="2">
       <c r="A253" t="s" s="35">
         <v>289</v>
       </c>
@@ -11722,7 +11722,7 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="254" hidden="false" outlineLevel="2">
+    <row r="254" hidden="true" outlineLevel="2">
       <c r="A254" t="s" s="35">
         <v>289</v>
       </c>
@@ -11763,7 +11763,7 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="255" hidden="false" outlineLevel="2">
+    <row r="255" hidden="true" outlineLevel="2">
       <c r="A255" t="s" s="35">
         <v>289</v>
       </c>
@@ -11804,7 +11804,7 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="256" hidden="false" outlineLevel="2">
+    <row r="256" hidden="true" outlineLevel="2">
       <c r="A256" t="s" s="35">
         <v>289</v>
       </c>
@@ -11845,7 +11845,7 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="257" hidden="false" outlineLevel="1">
+    <row r="257" hidden="true" outlineLevel="1">
       <c r="A257" t="s" s="23">
         <v>63</v>
       </c>
@@ -11872,7 +11872,7 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="258" hidden="false" outlineLevel="2">
+    <row r="258" hidden="true" outlineLevel="2">
       <c r="A258" t="s" s="35">
         <v>290</v>
       </c>
@@ -11913,7 +11913,7 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="259" hidden="false" outlineLevel="2">
+    <row r="259" hidden="true" outlineLevel="2">
       <c r="A259" t="s" s="35">
         <v>290</v>
       </c>
@@ -11954,7 +11954,7 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="260" hidden="false" outlineLevel="2">
+    <row r="260" hidden="true" outlineLevel="2">
       <c r="A260" t="s" s="35">
         <v>290</v>
       </c>
@@ -11995,7 +11995,7 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="261" hidden="false" outlineLevel="2">
+    <row r="261" hidden="true" outlineLevel="2">
       <c r="A261" t="s" s="35">
         <v>290</v>
       </c>
@@ -12036,7 +12036,7 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="262" hidden="false" outlineLevel="2">
+    <row r="262" hidden="true" outlineLevel="2">
       <c r="A262" t="s" s="35">
         <v>290</v>
       </c>
@@ -12077,7 +12077,7 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="263" hidden="false" outlineLevel="1">
+    <row r="263" hidden="true" outlineLevel="1">
       <c r="A263" t="s" s="23">
         <v>70</v>
       </c>
@@ -12104,7 +12104,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="264" hidden="false" outlineLevel="2">
+    <row r="264" hidden="true" outlineLevel="2">
       <c r="A264" t="s" s="35">
         <v>291</v>
       </c>
@@ -12145,7 +12145,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="265" hidden="false" outlineLevel="2">
+    <row r="265" hidden="true" outlineLevel="2">
       <c r="A265" t="s" s="35">
         <v>291</v>
       </c>
@@ -12186,7 +12186,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="266" hidden="false" outlineLevel="2">
+    <row r="266" hidden="true" outlineLevel="2">
       <c r="A266" t="s" s="35">
         <v>291</v>
       </c>
@@ -12227,7 +12227,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="267" hidden="false" outlineLevel="2">
+    <row r="267" hidden="true" outlineLevel="2">
       <c r="A267" t="s" s="35">
         <v>291</v>
       </c>
@@ -12268,7 +12268,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="268" hidden="false" outlineLevel="2">
+    <row r="268" hidden="true" outlineLevel="2">
       <c r="A268" t="s" s="35">
         <v>291</v>
       </c>
@@ -12309,7 +12309,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="269" hidden="false" outlineLevel="1">
+    <row r="269" hidden="true" outlineLevel="1">
       <c r="A269" t="s" s="23">
         <v>77</v>
       </c>
@@ -12336,7 +12336,7 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="270" hidden="false" outlineLevel="2">
+    <row r="270" hidden="true" outlineLevel="2">
       <c r="A270" t="s" s="35">
         <v>292</v>
       </c>
@@ -12377,7 +12377,7 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="271" hidden="false" outlineLevel="2">
+    <row r="271" hidden="true" outlineLevel="2">
       <c r="A271" t="s" s="35">
         <v>292</v>
       </c>
@@ -12418,7 +12418,7 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="272" hidden="false" outlineLevel="2">
+    <row r="272" hidden="true" outlineLevel="2">
       <c r="A272" t="s" s="35">
         <v>292</v>
       </c>
@@ -12459,7 +12459,7 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="273" hidden="false" outlineLevel="2">
+    <row r="273" hidden="true" outlineLevel="2">
       <c r="A273" t="s" s="35">
         <v>292</v>
       </c>
@@ -12500,7 +12500,7 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="274" hidden="false" outlineLevel="2">
+    <row r="274" hidden="true" outlineLevel="2">
       <c r="A274" t="s" s="35">
         <v>292</v>
       </c>
@@ -12541,7 +12541,7 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="275" hidden="false" outlineLevel="1">
+    <row r="275" hidden="true" outlineLevel="1">
       <c r="A275" t="s" s="23">
         <v>84</v>
       </c>
@@ -12568,7 +12568,7 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="276" hidden="false" outlineLevel="2">
+    <row r="276" hidden="true" outlineLevel="2">
       <c r="A276" t="s" s="35">
         <v>293</v>
       </c>
@@ -12609,7 +12609,7 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="277" hidden="false" outlineLevel="2">
+    <row r="277" hidden="true" outlineLevel="2">
       <c r="A277" t="s" s="35">
         <v>293</v>
       </c>
@@ -12650,7 +12650,7 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="278" hidden="false" outlineLevel="2">
+    <row r="278" hidden="true" outlineLevel="2">
       <c r="A278" t="s" s="35">
         <v>293</v>
       </c>
@@ -12691,7 +12691,7 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="279" hidden="false" outlineLevel="2">
+    <row r="279" hidden="true" outlineLevel="2">
       <c r="A279" t="s" s="35">
         <v>293</v>
       </c>
@@ -12732,7 +12732,7 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="280" hidden="false" outlineLevel="2">
+    <row r="280" hidden="true" outlineLevel="2">
       <c r="A280" t="s" s="35">
         <v>293</v>
       </c>
@@ -12773,7 +12773,7 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="281" hidden="false" outlineLevel="1">
+    <row r="281" hidden="true" outlineLevel="1">
       <c r="A281" t="s" s="23">
         <v>89</v>
       </c>
@@ -12800,7 +12800,7 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="282" hidden="false" outlineLevel="2">
+    <row r="282" hidden="true" outlineLevel="2">
       <c r="A282" t="s" s="35">
         <v>294</v>
       </c>
@@ -12841,7 +12841,7 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="283" hidden="false" outlineLevel="2">
+    <row r="283" hidden="true" outlineLevel="2">
       <c r="A283" t="s" s="35">
         <v>294</v>
       </c>
@@ -12882,7 +12882,7 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="284" hidden="false" outlineLevel="2">
+    <row r="284" hidden="true" outlineLevel="2">
       <c r="A284" t="s" s="35">
         <v>294</v>
       </c>
@@ -12923,7 +12923,7 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="285" hidden="false" outlineLevel="2">
+    <row r="285" hidden="true" outlineLevel="2">
       <c r="A285" t="s" s="35">
         <v>294</v>
       </c>
@@ -12964,7 +12964,7 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="286" hidden="false" outlineLevel="2">
+    <row r="286" hidden="true" outlineLevel="2">
       <c r="A286" t="s" s="35">
         <v>294</v>
       </c>
@@ -13005,7 +13005,7 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="287" hidden="false" outlineLevel="1">
+    <row r="287" hidden="true" outlineLevel="1">
       <c r="A287" t="s" s="23">
         <v>96</v>
       </c>
@@ -13032,7 +13032,7 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="288" hidden="false" outlineLevel="2">
+    <row r="288" hidden="true" outlineLevel="2">
       <c r="A288" t="s" s="35">
         <v>295</v>
       </c>
@@ -13073,7 +13073,7 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="289" hidden="false" outlineLevel="2">
+    <row r="289" hidden="true" outlineLevel="2">
       <c r="A289" t="s" s="35">
         <v>295</v>
       </c>
@@ -13114,7 +13114,7 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="290" hidden="false" outlineLevel="2">
+    <row r="290" hidden="true" outlineLevel="2">
       <c r="A290" t="s" s="35">
         <v>295</v>
       </c>
@@ -13155,7 +13155,7 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="291" hidden="false" outlineLevel="2">
+    <row r="291" hidden="true" outlineLevel="2">
       <c r="A291" t="s" s="35">
         <v>295</v>
       </c>
@@ -13196,7 +13196,7 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="292" hidden="false" outlineLevel="2">
+    <row r="292" hidden="true" outlineLevel="2">
       <c r="A292" t="s" s="35">
         <v>295</v>
       </c>
@@ -13237,7 +13237,7 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="293" hidden="false" outlineLevel="1">
+    <row r="293" hidden="true" outlineLevel="1">
       <c r="A293" t="s" s="23">
         <v>103</v>
       </c>
@@ -13264,7 +13264,7 @@
         <v>46412.0</v>
       </c>
     </row>
-    <row r="294" hidden="false" outlineLevel="2">
+    <row r="294" hidden="true" outlineLevel="2">
       <c r="A294" t="s" s="35">
         <v>296</v>
       </c>
@@ -13305,7 +13305,7 @@
         <v>46412.0</v>
       </c>
     </row>
-    <row r="295" hidden="false" outlineLevel="2">
+    <row r="295" hidden="true" outlineLevel="2">
       <c r="A295" t="s" s="35">
         <v>296</v>
       </c>
@@ -13346,7 +13346,7 @@
         <v>46412.0</v>
       </c>
     </row>
-    <row r="296" hidden="false" outlineLevel="2">
+    <row r="296" hidden="true" outlineLevel="2">
       <c r="A296" t="s" s="35">
         <v>296</v>
       </c>
@@ -13387,7 +13387,7 @@
         <v>46412.0</v>
       </c>
     </row>
-    <row r="297" hidden="false" outlineLevel="2">
+    <row r="297" hidden="true" outlineLevel="2">
       <c r="A297" t="s" s="35">
         <v>296</v>
       </c>
@@ -13428,7 +13428,7 @@
         <v>46412.0</v>
       </c>
     </row>
-    <row r="298" hidden="false" outlineLevel="2">
+    <row r="298" hidden="true" outlineLevel="2">
       <c r="A298" t="s" s="35">
         <v>296</v>
       </c>
@@ -13509,7 +13509,7 @@
       <c r="P300" s="81"/>
       <c r="Q300" s="81"/>
     </row>
-    <row r="301" hidden="false" outlineLevel="1">
+    <row r="301" hidden="true" outlineLevel="1">
       <c r="A301" s="21"/>
       <c r="B301" s="5"/>
       <c r="C301" s="7"/>
@@ -13528,7 +13528,7 @@
       <c r="P301" s="5"/>
       <c r="Q301" s="5"/>
     </row>
-    <row r="302" hidden="false" outlineLevel="1">
+    <row r="302" hidden="true" outlineLevel="1">
       <c r="A302" t="s" s="21">
         <v>298</v>
       </c>
@@ -13571,7 +13571,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="303" hidden="false" outlineLevel="1">
+    <row r="303" hidden="true" outlineLevel="1">
       <c r="A303" t="s" s="23">
         <v>302</v>
       </c>
@@ -13614,7 +13614,7 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="304" hidden="false" outlineLevel="1">
+    <row r="304" hidden="true" outlineLevel="1">
       <c r="A304" t="s" s="21">
         <v>303</v>
       </c>
@@ -13657,7 +13657,7 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="305" hidden="false" outlineLevel="1">
+    <row r="305" hidden="true" outlineLevel="1">
       <c r="A305" t="s" s="23">
         <v>304</v>
       </c>
@@ -13700,7 +13700,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="306" hidden="false" outlineLevel="1">
+    <row r="306" hidden="true" outlineLevel="1">
       <c r="A306" t="s" s="21">
         <v>305</v>
       </c>
@@ -13743,7 +13743,7 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="307" hidden="false" outlineLevel="1">
+    <row r="307" hidden="true" outlineLevel="1">
       <c r="A307" t="s" s="23">
         <v>306</v>
       </c>
@@ -13786,7 +13786,7 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="308" hidden="false" outlineLevel="1">
+    <row r="308" hidden="true" outlineLevel="1">
       <c r="A308" t="s" s="21">
         <v>307</v>
       </c>
@@ -13829,7 +13829,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="309" hidden="false" outlineLevel="1">
+    <row r="309" hidden="true" outlineLevel="1">
       <c r="A309" t="s" s="23">
         <v>308</v>
       </c>
@@ -13872,7 +13872,7 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="310" hidden="false" outlineLevel="1">
+    <row r="310" hidden="true" outlineLevel="1">
       <c r="A310" t="s" s="21">
         <v>309</v>
       </c>
@@ -13915,7 +13915,7 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="311" hidden="false" outlineLevel="1">
+    <row r="311" hidden="true" outlineLevel="1">
       <c r="A311" t="s" s="23">
         <v>310</v>
       </c>
@@ -13958,7 +13958,7 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="312" hidden="false" outlineLevel="1">
+    <row r="312" hidden="true" outlineLevel="1">
       <c r="A312" t="s" s="21">
         <v>311</v>
       </c>
@@ -14001,7 +14001,7 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="313" hidden="false" outlineLevel="1">
+    <row r="313" hidden="true" outlineLevel="1">
       <c r="A313" t="s" s="23">
         <v>312</v>
       </c>
@@ -14084,7 +14084,7 @@
       <c r="P315" s="81"/>
       <c r="Q315" s="81"/>
     </row>
-    <row r="316" hidden="false" outlineLevel="1">
+    <row r="316" hidden="true" outlineLevel="1">
       <c r="A316" s="21"/>
       <c r="B316" s="5"/>
       <c r="C316" s="7"/>
@@ -14103,7 +14103,7 @@
       <c r="P316" s="5"/>
       <c r="Q316" s="5"/>
     </row>
-    <row r="317" hidden="false" outlineLevel="1">
+    <row r="317" hidden="true" outlineLevel="1">
       <c r="A317" t="s" s="23">
         <v>19</v>
       </c>
@@ -14144,7 +14144,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="318" hidden="false" outlineLevel="2">
+    <row r="318" hidden="true" outlineLevel="2">
       <c r="A318" t="s" s="35">
         <v>316</v>
       </c>
@@ -14187,7 +14187,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="319" hidden="false" outlineLevel="2">
+    <row r="319" hidden="true" outlineLevel="2">
       <c r="A319" t="s" s="35">
         <v>316</v>
       </c>
@@ -14230,7 +14230,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="320" hidden="false" outlineLevel="2">
+    <row r="320" hidden="true" outlineLevel="2">
       <c r="A320" t="s" s="35">
         <v>316</v>
       </c>
@@ -14273,7 +14273,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="321" hidden="false" outlineLevel="2">
+    <row r="321" hidden="true" outlineLevel="2">
       <c r="A321" t="s" s="35">
         <v>316</v>
       </c>
@@ -14316,7 +14316,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="322" hidden="false" outlineLevel="2">
+    <row r="322" hidden="true" outlineLevel="2">
       <c r="A322" t="s" s="35">
         <v>316</v>
       </c>
@@ -14359,7 +14359,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="323" hidden="false" outlineLevel="2">
+    <row r="323" hidden="true" outlineLevel="2">
       <c r="A323" t="s" s="35">
         <v>316</v>
       </c>

--- a/03. CMH120 OFCI Log REV2.0.xlsx
+++ b/03. CMH120 OFCI Log REV2.0.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6127" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6126" uniqueCount="463">
   <si>
     <t/>
   </si>
@@ -949,7 +949,7 @@
     <t>april.kruger@interstates.com</t>
   </si>
   <si>
-    <t>DLB As Well OSA Delivery - 12/8/2025</t>
+    <t>DLB Delivered on to OSA - 12/11/2025/AMCOP Delivered on to OSA 12/15/2025</t>
   </si>
   <si>
     <t>ROMP 02 AMCOP</t>
@@ -6516,11 +6516,11 @@
       <c r="F119" t="s" s="59">
         <v>165</v>
       </c>
-      <c r="G119" t="n" s="39">
+      <c r="G119" t="n" s="61">
         <v>46027.0</v>
       </c>
       <c r="H119" t="n" s="61">
-        <v>46027.0</v>
+        <v>46076.0</v>
       </c>
       <c r="I119" t="n" s="61">
         <v>46062.0</v>
@@ -6528,8 +6528,8 @@
       <c r="J119" t="n" s="41">
         <v>46027.0</v>
       </c>
-      <c r="K119" t="n" s="11">
-        <v>35.0</v>
+      <c r="K119" t="n" s="63">
+        <v>-14.0</v>
       </c>
       <c r="L119" s="7"/>
       <c r="M119" s="7"/>
@@ -6565,7 +6565,7 @@
         <v>46083.0</v>
       </c>
       <c r="H120" t="n" s="31">
-        <v>46083.0</v>
+        <v>46090.0</v>
       </c>
       <c r="I120" t="n" s="31">
         <v>46139.0</v>
@@ -6574,7 +6574,7 @@
         <v>46083.0</v>
       </c>
       <c r="K120" t="n" s="27">
-        <v>56.0</v>
+        <v>49.0</v>
       </c>
       <c r="L120" s="27"/>
       <c r="M120" s="27"/>
@@ -6610,7 +6610,7 @@
         <v>46111.0</v>
       </c>
       <c r="H121" t="n" s="61">
-        <v>46111.0</v>
+        <v>46104.0</v>
       </c>
       <c r="I121" t="n" s="61">
         <v>46167.0</v>
@@ -6619,7 +6619,7 @@
         <v>46111.0</v>
       </c>
       <c r="K121" t="n" s="11">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
       <c r="L121" s="7"/>
       <c r="M121" s="7"/>
@@ -6655,7 +6655,7 @@
         <v>46129.0</v>
       </c>
       <c r="H122" t="n" s="31">
-        <v>46129.0</v>
+        <v>46118.0</v>
       </c>
       <c r="I122" t="n" s="31">
         <v>46195.0</v>
@@ -6664,7 +6664,7 @@
         <v>46139.0</v>
       </c>
       <c r="K122" t="n" s="27">
-        <v>66.0</v>
+        <v>77.0</v>
       </c>
       <c r="L122" s="27"/>
       <c r="M122" s="27"/>
@@ -6700,7 +6700,7 @@
         <v>46143.0</v>
       </c>
       <c r="H123" t="n" s="61">
-        <v>46143.0</v>
+        <v>46132.0</v>
       </c>
       <c r="I123" t="n" s="61">
         <v>46223.0</v>
@@ -6709,7 +6709,7 @@
         <v>46167.0</v>
       </c>
       <c r="K123" t="n" s="11">
-        <v>80.0</v>
+        <v>91.0</v>
       </c>
       <c r="L123" s="7"/>
       <c r="M123" s="7"/>
@@ -6745,7 +6745,7 @@
         <v>46157.0</v>
       </c>
       <c r="H124" t="n" s="31">
-        <v>46157.0</v>
+        <v>46146.0</v>
       </c>
       <c r="I124" t="n" s="31">
         <v>46251.0</v>
@@ -6754,7 +6754,7 @@
         <v>46195.0</v>
       </c>
       <c r="K124" t="n" s="27">
-        <v>94.0</v>
+        <v>105.0</v>
       </c>
       <c r="L124" s="27"/>
       <c r="M124" s="27"/>
@@ -6790,7 +6790,7 @@
         <v>46175.0</v>
       </c>
       <c r="H125" t="n" s="61">
-        <v>46175.0</v>
+        <v>46160.0</v>
       </c>
       <c r="I125" t="n" s="61">
         <v>46279.0</v>
@@ -6799,7 +6799,7 @@
         <v>46223.0</v>
       </c>
       <c r="K125" t="n" s="11">
-        <v>104.0</v>
+        <v>119.0</v>
       </c>
       <c r="L125" s="7"/>
       <c r="M125" s="7"/>
@@ -6835,7 +6835,7 @@
         <v>46192.0</v>
       </c>
       <c r="H126" t="n" s="31">
-        <v>46192.0</v>
+        <v>46174.0</v>
       </c>
       <c r="I126" t="n" s="31">
         <v>46307.0</v>
@@ -6844,7 +6844,7 @@
         <v>46251.0</v>
       </c>
       <c r="K126" t="n" s="27">
-        <v>115.0</v>
+        <v>133.0</v>
       </c>
       <c r="L126" s="27"/>
       <c r="M126" s="27"/>
@@ -6880,7 +6880,7 @@
         <v>46206.0</v>
       </c>
       <c r="H127" t="n" s="61">
-        <v>46206.0</v>
+        <v>46188.0</v>
       </c>
       <c r="I127" t="n" s="61">
         <v>46335.0</v>
@@ -6889,7 +6889,7 @@
         <v>46279.0</v>
       </c>
       <c r="K127" t="n" s="11">
-        <v>129.0</v>
+        <v>147.0</v>
       </c>
       <c r="L127" s="7"/>
       <c r="M127" s="7"/>
@@ -6925,7 +6925,7 @@
         <v>46220.0</v>
       </c>
       <c r="H128" t="n" s="31">
-        <v>46220.0</v>
+        <v>46202.0</v>
       </c>
       <c r="I128" t="n" s="31">
         <v>46363.0</v>
@@ -6934,7 +6934,7 @@
         <v>46307.0</v>
       </c>
       <c r="K128" t="n" s="27">
-        <v>143.0</v>
+        <v>161.0</v>
       </c>
       <c r="L128" s="27"/>
       <c r="M128" s="27"/>
@@ -6970,7 +6970,7 @@
         <v>46234.0</v>
       </c>
       <c r="H129" t="n" s="61">
-        <v>46234.0</v>
+        <v>46216.0</v>
       </c>
       <c r="I129" t="n" s="61">
         <v>46391.0</v>
@@ -6979,7 +6979,7 @@
         <v>46335.0</v>
       </c>
       <c r="K129" t="n" s="11">
-        <v>157.0</v>
+        <v>175.0</v>
       </c>
       <c r="L129" s="7"/>
       <c r="M129" s="7"/>
@@ -7015,7 +7015,7 @@
         <v>46248.0</v>
       </c>
       <c r="H130" t="n" s="31">
-        <v>46248.0</v>
+        <v>46230.0</v>
       </c>
       <c r="I130" t="n" s="31">
         <v>46419.0</v>
@@ -7024,7 +7024,7 @@
         <v>46363.0</v>
       </c>
       <c r="K130" t="n" s="27">
-        <v>171.0</v>
+        <v>189.0</v>
       </c>
       <c r="L130" s="27"/>
       <c r="M130" s="27"/>
@@ -7077,7 +7077,7 @@
       <c r="P132" s="15"/>
       <c r="Q132" s="15"/>
     </row>
-    <row r="133" hidden="true" outlineLevel="1">
+    <row r="133" hidden="false" outlineLevel="1">
       <c r="A133" s="21"/>
       <c r="B133" s="5"/>
       <c r="C133" s="7"/>
@@ -7096,7 +7096,7 @@
       <c r="P133" s="5"/>
       <c r="Q133" s="5"/>
     </row>
-    <row r="134" hidden="true" outlineLevel="1">
+    <row r="134" hidden="false" outlineLevel="1">
       <c r="A134" t="s" s="23">
         <v>19</v>
       </c>
@@ -7135,7 +7135,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="135" hidden="true" outlineLevel="2">
+    <row r="135" hidden="false" outlineLevel="2">
       <c r="A135" t="s" s="35">
         <v>169</v>
       </c>
@@ -7176,7 +7176,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="136" hidden="true" outlineLevel="2">
+    <row r="136" hidden="false" outlineLevel="2">
       <c r="A136" t="s" s="35">
         <v>169</v>
       </c>
@@ -7217,7 +7217,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="137" hidden="true" outlineLevel="2">
+    <row r="137" hidden="false" outlineLevel="2">
       <c r="A137" t="s" s="35">
         <v>169</v>
       </c>
@@ -7258,7 +7258,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="138" hidden="true" outlineLevel="2">
+    <row r="138" hidden="false" outlineLevel="2">
       <c r="A138" t="s" s="35">
         <v>169</v>
       </c>
@@ -7299,7 +7299,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="139" hidden="true" outlineLevel="2">
+    <row r="139" hidden="false" outlineLevel="2">
       <c r="A139" t="s" s="35">
         <v>169</v>
       </c>
@@ -7340,7 +7340,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="140" hidden="true" outlineLevel="2">
+    <row r="140" hidden="false" outlineLevel="2">
       <c r="A140" t="s" s="35">
         <v>169</v>
       </c>
@@ -8020,7 +8020,7 @@
       <c r="P157" s="15"/>
       <c r="Q157" s="15"/>
     </row>
-    <row r="158" hidden="false" outlineLevel="1">
+    <row r="158" hidden="true" outlineLevel="1">
       <c r="A158" s="21"/>
       <c r="B158" s="5"/>
       <c r="C158" s="7"/>
@@ -8041,7 +8041,7 @@
       <c r="P158" s="5"/>
       <c r="Q158" s="5"/>
     </row>
-    <row r="159" hidden="false" outlineLevel="1">
+    <row r="159" hidden="true" outlineLevel="1">
       <c r="A159" t="s" s="45">
         <v>193</v>
       </c>
@@ -8086,7 +8086,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="160" hidden="false" outlineLevel="1">
+    <row r="160" hidden="true" outlineLevel="1">
       <c r="A160" t="s" s="45">
         <v>197</v>
       </c>
@@ -8131,39 +8131,41 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="161" hidden="false" outlineLevel="1">
-      <c r="A161" t="s" s="21">
+    <row r="161" hidden="true" outlineLevel="1">
+      <c r="A161" t="s" s="45">
         <v>199</v>
       </c>
-      <c r="B161" t="s" s="5">
+      <c r="B161" t="s" s="47">
         <v>44</v>
       </c>
-      <c r="C161" t="s" s="7">
+      <c r="C161" t="s" s="49">
         <v>194</v>
       </c>
-      <c r="D161" t="s" s="7">
+      <c r="D161" t="s" s="49">
         <v>33</v>
       </c>
-      <c r="E161" t="s" s="7">
+      <c r="E161" t="s" s="49">
         <v>195</v>
       </c>
-      <c r="F161" t="s" s="9">
+      <c r="F161" t="s" s="51">
         <v>196</v>
       </c>
-      <c r="G161" s="57"/>
-      <c r="H161" t="n" s="41">
+      <c r="G161" s="49"/>
+      <c r="H161" t="n" s="53">
         <v>46004.0</v>
       </c>
-      <c r="I161" t="n" s="41">
+      <c r="I161" t="n" s="53">
         <v>46174.0</v>
       </c>
       <c r="J161" t="n" s="41">
         <v>46034.0</v>
       </c>
-      <c r="K161" t="n" s="7">
+      <c r="K161" t="n" s="49">
         <v>170.0</v>
       </c>
-      <c r="L161" s="7"/>
+      <c r="L161" t="n" s="53">
+        <v>46004.0</v>
+      </c>
       <c r="M161" s="7"/>
       <c r="N161" s="7"/>
       <c r="O161" t="s" s="7">
@@ -8174,7 +8176,7 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="162" hidden="false" outlineLevel="1">
+    <row r="162" hidden="true" outlineLevel="1">
       <c r="A162" t="s" s="23">
         <v>200</v>
       </c>
@@ -8217,7 +8219,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="163" hidden="false" outlineLevel="1">
+    <row r="163" hidden="true" outlineLevel="1">
       <c r="A163" t="s" s="21">
         <v>201</v>
       </c>
@@ -8260,7 +8262,7 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="164" hidden="false" outlineLevel="1">
+    <row r="164" hidden="true" outlineLevel="1">
       <c r="A164" t="s" s="23">
         <v>202</v>
       </c>
@@ -8303,7 +8305,7 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="165" hidden="false" outlineLevel="1">
+    <row r="165" hidden="true" outlineLevel="1">
       <c r="A165" t="s" s="21">
         <v>203</v>
       </c>
@@ -8346,7 +8348,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="166" hidden="false" outlineLevel="1">
+    <row r="166" hidden="true" outlineLevel="1">
       <c r="A166" t="s" s="23">
         <v>204</v>
       </c>
@@ -8389,7 +8391,7 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="167" hidden="false" outlineLevel="1">
+    <row r="167" hidden="true" outlineLevel="1">
       <c r="A167" t="s" s="21">
         <v>205</v>
       </c>
@@ -8432,7 +8434,7 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="168" hidden="false" outlineLevel="1">
+    <row r="168" hidden="true" outlineLevel="1">
       <c r="A168" t="s" s="23">
         <v>206</v>
       </c>
@@ -8475,7 +8477,7 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="169" hidden="false" outlineLevel="1">
+    <row r="169" hidden="true" outlineLevel="1">
       <c r="A169" t="s" s="21">
         <v>207</v>
       </c>
@@ -8518,7 +8520,7 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="170" hidden="false" outlineLevel="1">
+    <row r="170" hidden="true" outlineLevel="1">
       <c r="A170" t="s" s="23">
         <v>208</v>
       </c>
@@ -10420,7 +10422,7 @@
       <c r="P219" s="81"/>
       <c r="Q219" s="81"/>
     </row>
-    <row r="220" hidden="true" outlineLevel="1">
+    <row r="220" hidden="false" outlineLevel="1">
       <c r="A220" s="21"/>
       <c r="B220" s="5"/>
       <c r="C220" s="7"/>
@@ -10439,7 +10441,7 @@
       <c r="P220" s="5"/>
       <c r="Q220" s="5"/>
     </row>
-    <row r="221" hidden="true" outlineLevel="1">
+    <row r="221" hidden="false" outlineLevel="1">
       <c r="A221" t="s" s="21">
         <v>261</v>
       </c>
@@ -10460,7 +10462,7 @@
         <v>46027.0</v>
       </c>
       <c r="H221" t="n" s="41">
-        <v>46041.0</v>
+        <v>46066.0</v>
       </c>
       <c r="I221" t="n" s="41">
         <v>46069.0</v>
@@ -10482,7 +10484,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="222" hidden="true" outlineLevel="1">
+    <row r="222" hidden="false" outlineLevel="1">
       <c r="A222" t="s" s="23">
         <v>265</v>
       </c>
@@ -10503,7 +10505,7 @@
         <v>46097.0</v>
       </c>
       <c r="H222" t="n" s="31">
-        <v>46097.0</v>
+        <v>46108.0</v>
       </c>
       <c r="I222" t="n" s="41">
         <v>46146.0</v>
@@ -10525,7 +10527,7 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="223" hidden="true" outlineLevel="1">
+    <row r="223" hidden="false" outlineLevel="1">
       <c r="A223" t="s" s="21">
         <v>268</v>
       </c>
@@ -10546,7 +10548,7 @@
         <v>46111.0</v>
       </c>
       <c r="H223" t="n" s="41">
-        <v>46111.0</v>
+        <v>46115.0</v>
       </c>
       <c r="I223" t="n" s="41">
         <v>46174.0</v>
@@ -10568,7 +10570,7 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="224" hidden="true" outlineLevel="1">
+    <row r="224" hidden="false" outlineLevel="1">
       <c r="A224" t="s" s="23">
         <v>269</v>
       </c>
@@ -10611,7 +10613,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="225" hidden="true" outlineLevel="1">
+    <row r="225" hidden="false" outlineLevel="1">
       <c r="A225" t="s" s="21">
         <v>271</v>
       </c>
@@ -10654,7 +10656,7 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="226" hidden="true" outlineLevel="1">
+    <row r="226" hidden="false" outlineLevel="1">
       <c r="A226" t="s" s="23">
         <v>273</v>
       </c>
@@ -10697,7 +10699,7 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="227" hidden="true" outlineLevel="1">
+    <row r="227" hidden="false" outlineLevel="1">
       <c r="A227" t="s" s="21">
         <v>275</v>
       </c>
@@ -10740,7 +10742,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="228" hidden="true" outlineLevel="1">
+    <row r="228" hidden="false" outlineLevel="1">
       <c r="A228" t="s" s="23">
         <v>277</v>
       </c>
@@ -10783,7 +10785,7 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="229" hidden="true" outlineLevel="1">
+    <row r="229" hidden="false" outlineLevel="1">
       <c r="A229" t="s" s="21">
         <v>279</v>
       </c>
@@ -10826,7 +10828,7 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="230" hidden="true" outlineLevel="1">
+    <row r="230" hidden="false" outlineLevel="1">
       <c r="A230" t="s" s="23">
         <v>281</v>
       </c>
@@ -10869,7 +10871,7 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="231" hidden="true" outlineLevel="1">
+    <row r="231" hidden="false" outlineLevel="1">
       <c r="A231" t="s" s="21">
         <v>283</v>
       </c>
@@ -10912,7 +10914,7 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="232" hidden="true" outlineLevel="1">
+    <row r="232" hidden="false" outlineLevel="1">
       <c r="A232" t="s" s="23">
         <v>285</v>
       </c>
@@ -10995,7 +10997,7 @@
       <c r="P234" s="81"/>
       <c r="Q234" s="81"/>
     </row>
-    <row r="235" hidden="true" outlineLevel="1">
+    <row r="235" hidden="false" outlineLevel="1">
       <c r="A235" s="21"/>
       <c r="B235" s="5"/>
       <c r="C235" s="7"/>
@@ -11014,7 +11016,7 @@
       <c r="P235" s="5"/>
       <c r="Q235" s="5"/>
     </row>
-    <row r="236" hidden="true" outlineLevel="1">
+    <row r="236" hidden="false" outlineLevel="1">
       <c r="A236" t="s" s="23">
         <v>19</v>
       </c>
@@ -11043,7 +11045,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="237" hidden="true" outlineLevel="2">
+    <row r="237" hidden="false" outlineLevel="2">
       <c r="A237" t="s" s="35">
         <v>288</v>
       </c>
@@ -11066,7 +11068,7 @@
         <v>46027.0</v>
       </c>
       <c r="H237" t="n" s="41">
-        <v>46041.0</v>
+        <v>46066.0</v>
       </c>
       <c r="I237" s="7"/>
       <c r="J237" t="n" s="41">
@@ -11084,7 +11086,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="238" hidden="true" outlineLevel="2">
+    <row r="238" hidden="false" outlineLevel="2">
       <c r="A238" t="s" s="35">
         <v>288</v>
       </c>
@@ -11107,7 +11109,7 @@
         <v>46027.0</v>
       </c>
       <c r="H238" t="n" s="41">
-        <v>46041.0</v>
+        <v>46066.0</v>
       </c>
       <c r="I238" s="7"/>
       <c r="J238" t="n" s="41">
@@ -11125,7 +11127,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="239" hidden="true" outlineLevel="2">
+    <row r="239" hidden="false" outlineLevel="2">
       <c r="A239" t="s" s="35">
         <v>288</v>
       </c>
@@ -11148,7 +11150,7 @@
         <v>46027.0</v>
       </c>
       <c r="H239" t="n" s="41">
-        <v>46041.0</v>
+        <v>46066.0</v>
       </c>
       <c r="I239" s="7"/>
       <c r="J239" t="n" s="41">
@@ -11166,7 +11168,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="240" hidden="true" outlineLevel="2">
+    <row r="240" hidden="false" outlineLevel="2">
       <c r="A240" t="s" s="35">
         <v>288</v>
       </c>
@@ -11189,7 +11191,7 @@
         <v>46027.0</v>
       </c>
       <c r="H240" t="n" s="41">
-        <v>46041.0</v>
+        <v>46066.0</v>
       </c>
       <c r="I240" s="7"/>
       <c r="J240" t="n" s="41">
@@ -11207,7 +11209,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="241" hidden="true" outlineLevel="2">
+    <row r="241" hidden="false" outlineLevel="2">
       <c r="A241" t="s" s="35">
         <v>288</v>
       </c>
@@ -11230,7 +11232,7 @@
         <v>46027.0</v>
       </c>
       <c r="H241" t="n" s="41">
-        <v>46041.0</v>
+        <v>46066.0</v>
       </c>
       <c r="I241" s="7"/>
       <c r="J241" t="n" s="41">
@@ -11248,7 +11250,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="242" hidden="true" outlineLevel="1">
+    <row r="242" hidden="false" outlineLevel="1">
       <c r="A242" t="s" s="23">
         <v>35</v>
       </c>
@@ -11275,7 +11277,7 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="243" hidden="true" outlineLevel="2">
+    <row r="243" hidden="false" outlineLevel="2">
       <c r="A243" t="s" s="35">
         <v>296</v>
       </c>
@@ -11297,8 +11299,8 @@
       <c r="G243" t="n" s="31">
         <v>46097.0</v>
       </c>
-      <c r="H243" t="n" s="61">
-        <v>46097.0</v>
+      <c r="H243" t="n" s="31">
+        <v>46108.0</v>
       </c>
       <c r="I243" s="7"/>
       <c r="J243" t="n" s="41">
@@ -11316,7 +11318,7 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="244" hidden="true" outlineLevel="2">
+    <row r="244" hidden="false" outlineLevel="2">
       <c r="A244" t="s" s="35">
         <v>296</v>
       </c>
@@ -11338,8 +11340,8 @@
       <c r="G244" t="n" s="31">
         <v>46097.0</v>
       </c>
-      <c r="H244" t="n" s="61">
-        <v>46097.0</v>
+      <c r="H244" t="n" s="31">
+        <v>46108.0</v>
       </c>
       <c r="I244" s="7"/>
       <c r="J244" t="n" s="41">
@@ -11357,7 +11359,7 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="245" hidden="true" outlineLevel="2">
+    <row r="245" hidden="false" outlineLevel="2">
       <c r="A245" t="s" s="35">
         <v>296</v>
       </c>
@@ -11379,8 +11381,8 @@
       <c r="G245" t="n" s="31">
         <v>46097.0</v>
       </c>
-      <c r="H245" t="n" s="61">
-        <v>46097.0</v>
+      <c r="H245" t="n" s="31">
+        <v>46108.0</v>
       </c>
       <c r="I245" s="7"/>
       <c r="J245" t="n" s="41">
@@ -11398,7 +11400,7 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="246" hidden="true" outlineLevel="2">
+    <row r="246" hidden="false" outlineLevel="2">
       <c r="A246" t="s" s="35">
         <v>296</v>
       </c>
@@ -11420,8 +11422,8 @@
       <c r="G246" t="n" s="31">
         <v>46097.0</v>
       </c>
-      <c r="H246" t="n" s="61">
-        <v>46097.0</v>
+      <c r="H246" t="n" s="31">
+        <v>46108.0</v>
       </c>
       <c r="I246" s="7"/>
       <c r="J246" t="n" s="41">
@@ -11439,7 +11441,7 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="247" hidden="true" outlineLevel="2">
+    <row r="247" hidden="false" outlineLevel="2">
       <c r="A247" t="s" s="35">
         <v>296</v>
       </c>
@@ -11461,8 +11463,8 @@
       <c r="G247" t="n" s="31">
         <v>46097.0</v>
       </c>
-      <c r="H247" t="n" s="61">
-        <v>46097.0</v>
+      <c r="H247" t="n" s="31">
+        <v>46108.0</v>
       </c>
       <c r="I247" s="7"/>
       <c r="J247" t="n" s="41">
@@ -11480,7 +11482,7 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="248" hidden="true" outlineLevel="1">
+    <row r="248" hidden="false" outlineLevel="1">
       <c r="A248" t="s" s="23">
         <v>42</v>
       </c>
@@ -11507,7 +11509,7 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="249" hidden="true" outlineLevel="2">
+    <row r="249" hidden="false" outlineLevel="2">
       <c r="A249" t="s" s="35">
         <v>297</v>
       </c>
@@ -11530,7 +11532,7 @@
         <v>46111.0</v>
       </c>
       <c r="H249" t="n" s="41">
-        <v>46111.0</v>
+        <v>46115.0</v>
       </c>
       <c r="I249" s="7"/>
       <c r="J249" t="n" s="41">
@@ -11548,7 +11550,7 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="250" hidden="true" outlineLevel="2">
+    <row r="250" hidden="false" outlineLevel="2">
       <c r="A250" t="s" s="35">
         <v>297</v>
       </c>
@@ -11571,7 +11573,7 @@
         <v>46111.0</v>
       </c>
       <c r="H250" t="n" s="41">
-        <v>46111.0</v>
+        <v>46115.0</v>
       </c>
       <c r="I250" s="7"/>
       <c r="J250" t="n" s="41">
@@ -11589,7 +11591,7 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="251" hidden="true" outlineLevel="2">
+    <row r="251" hidden="false" outlineLevel="2">
       <c r="A251" t="s" s="35">
         <v>297</v>
       </c>
@@ -11612,7 +11614,7 @@
         <v>46111.0</v>
       </c>
       <c r="H251" t="n" s="41">
-        <v>46111.0</v>
+        <v>46115.0</v>
       </c>
       <c r="I251" s="7"/>
       <c r="J251" t="n" s="41">
@@ -11630,7 +11632,7 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="252" hidden="true" outlineLevel="2">
+    <row r="252" hidden="false" outlineLevel="2">
       <c r="A252" t="s" s="35">
         <v>297</v>
       </c>
@@ -11653,7 +11655,7 @@
         <v>46111.0</v>
       </c>
       <c r="H252" t="n" s="41">
-        <v>46111.0</v>
+        <v>46115.0</v>
       </c>
       <c r="I252" s="7"/>
       <c r="J252" t="n" s="41">
@@ -11671,7 +11673,7 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="253" hidden="true" outlineLevel="2">
+    <row r="253" hidden="false" outlineLevel="2">
       <c r="A253" t="s" s="35">
         <v>297</v>
       </c>
@@ -11694,7 +11696,7 @@
         <v>46111.0</v>
       </c>
       <c r="H253" t="n" s="41">
-        <v>46111.0</v>
+        <v>46115.0</v>
       </c>
       <c r="I253" s="7"/>
       <c r="J253" t="n" s="41">
@@ -11712,7 +11714,7 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="254" hidden="true" outlineLevel="1">
+    <row r="254" hidden="false" outlineLevel="1">
       <c r="A254" t="s" s="23">
         <v>49</v>
       </c>
@@ -11739,7 +11741,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="255" hidden="true" outlineLevel="2">
+    <row r="255" hidden="false" outlineLevel="2">
       <c r="A255" t="s" s="35">
         <v>298</v>
       </c>
@@ -11761,8 +11763,8 @@
       <c r="G255" t="n" s="31">
         <v>46129.0</v>
       </c>
-      <c r="H255" t="n" s="61">
-        <v>46129.0</v>
+      <c r="H255" t="n" s="31">
+        <v>46125.0</v>
       </c>
       <c r="I255" s="7"/>
       <c r="J255" t="n" s="41">
@@ -11780,7 +11782,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="256" hidden="true" outlineLevel="2">
+    <row r="256" hidden="false" outlineLevel="2">
       <c r="A256" t="s" s="35">
         <v>298</v>
       </c>
@@ -11802,8 +11804,8 @@
       <c r="G256" t="n" s="31">
         <v>46129.0</v>
       </c>
-      <c r="H256" t="n" s="61">
-        <v>46129.0</v>
+      <c r="H256" t="n" s="31">
+        <v>46125.0</v>
       </c>
       <c r="I256" s="7"/>
       <c r="J256" t="n" s="41">
@@ -11821,7 +11823,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="257" hidden="true" outlineLevel="2">
+    <row r="257" hidden="false" outlineLevel="2">
       <c r="A257" t="s" s="35">
         <v>298</v>
       </c>
@@ -11843,8 +11845,8 @@
       <c r="G257" t="n" s="31">
         <v>46129.0</v>
       </c>
-      <c r="H257" t="n" s="61">
-        <v>46129.0</v>
+      <c r="H257" t="n" s="31">
+        <v>46125.0</v>
       </c>
       <c r="I257" s="7"/>
       <c r="J257" t="n" s="41">
@@ -11862,7 +11864,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="258" hidden="true" outlineLevel="2">
+    <row r="258" hidden="false" outlineLevel="2">
       <c r="A258" t="s" s="35">
         <v>298</v>
       </c>
@@ -11884,8 +11886,8 @@
       <c r="G258" t="n" s="31">
         <v>46129.0</v>
       </c>
-      <c r="H258" t="n" s="61">
-        <v>46129.0</v>
+      <c r="H258" t="n" s="31">
+        <v>46125.0</v>
       </c>
       <c r="I258" s="7"/>
       <c r="J258" t="n" s="41">
@@ -11903,7 +11905,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="259" hidden="true" outlineLevel="2">
+    <row r="259" hidden="false" outlineLevel="2">
       <c r="A259" t="s" s="35">
         <v>298</v>
       </c>
@@ -11925,8 +11927,8 @@
       <c r="G259" t="n" s="31">
         <v>46129.0</v>
       </c>
-      <c r="H259" t="n" s="61">
-        <v>46129.0</v>
+      <c r="H259" t="n" s="31">
+        <v>46125.0</v>
       </c>
       <c r="I259" s="7"/>
       <c r="J259" t="n" s="41">
@@ -11944,7 +11946,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="260" hidden="true" outlineLevel="1">
+    <row r="260" hidden="false" outlineLevel="1">
       <c r="A260" t="s" s="23">
         <v>56</v>
       </c>
@@ -11971,7 +11973,7 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="261" hidden="true" outlineLevel="2">
+    <row r="261" hidden="false" outlineLevel="2">
       <c r="A261" t="s" s="35">
         <v>299</v>
       </c>
@@ -11994,7 +11996,7 @@
         <v>46143.0</v>
       </c>
       <c r="H261" t="n" s="41">
-        <v>46143.0</v>
+        <v>46139.0</v>
       </c>
       <c r="I261" s="7"/>
       <c r="J261" t="n" s="41">
@@ -12012,7 +12014,7 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="262" hidden="true" outlineLevel="2">
+    <row r="262" hidden="false" outlineLevel="2">
       <c r="A262" t="s" s="35">
         <v>299</v>
       </c>
@@ -12035,7 +12037,7 @@
         <v>46143.0</v>
       </c>
       <c r="H262" t="n" s="41">
-        <v>46143.0</v>
+        <v>46139.0</v>
       </c>
       <c r="I262" s="7"/>
       <c r="J262" t="n" s="41">
@@ -12053,7 +12055,7 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="263" hidden="true" outlineLevel="2">
+    <row r="263" hidden="false" outlineLevel="2">
       <c r="A263" t="s" s="35">
         <v>299</v>
       </c>
@@ -12076,7 +12078,7 @@
         <v>46143.0</v>
       </c>
       <c r="H263" t="n" s="41">
-        <v>46143.0</v>
+        <v>46139.0</v>
       </c>
       <c r="I263" s="7"/>
       <c r="J263" t="n" s="41">
@@ -12094,7 +12096,7 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="264" hidden="true" outlineLevel="2">
+    <row r="264" hidden="false" outlineLevel="2">
       <c r="A264" t="s" s="35">
         <v>299</v>
       </c>
@@ -12117,7 +12119,7 @@
         <v>46143.0</v>
       </c>
       <c r="H264" t="n" s="41">
-        <v>46143.0</v>
+        <v>46139.0</v>
       </c>
       <c r="I264" s="7"/>
       <c r="J264" t="n" s="41">
@@ -12135,7 +12137,7 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="265" hidden="true" outlineLevel="2">
+    <row r="265" hidden="false" outlineLevel="2">
       <c r="A265" t="s" s="35">
         <v>299</v>
       </c>
@@ -12158,7 +12160,7 @@
         <v>46143.0</v>
       </c>
       <c r="H265" t="n" s="41">
-        <v>46143.0</v>
+        <v>46139.0</v>
       </c>
       <c r="I265" s="7"/>
       <c r="J265" t="n" s="41">
@@ -12176,7 +12178,7 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="266" hidden="true" outlineLevel="1">
+    <row r="266" hidden="false" outlineLevel="1">
       <c r="A266" t="s" s="23">
         <v>63</v>
       </c>
@@ -12203,7 +12205,7 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="267" hidden="true" outlineLevel="2">
+    <row r="267" hidden="false" outlineLevel="2">
       <c r="A267" t="s" s="35">
         <v>300</v>
       </c>
@@ -12225,8 +12227,8 @@
       <c r="G267" t="n" s="31">
         <v>46157.0</v>
       </c>
-      <c r="H267" t="n" s="61">
-        <v>46157.0</v>
+      <c r="H267" t="n" s="31">
+        <v>46153.0</v>
       </c>
       <c r="I267" s="7"/>
       <c r="J267" t="n" s="41">
@@ -12244,7 +12246,7 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="268" hidden="true" outlineLevel="2">
+    <row r="268" hidden="false" outlineLevel="2">
       <c r="A268" t="s" s="35">
         <v>300</v>
       </c>
@@ -12266,8 +12268,8 @@
       <c r="G268" t="n" s="31">
         <v>46157.0</v>
       </c>
-      <c r="H268" t="n" s="61">
-        <v>46157.0</v>
+      <c r="H268" t="n" s="31">
+        <v>46153.0</v>
       </c>
       <c r="I268" s="7"/>
       <c r="J268" t="n" s="41">
@@ -12285,7 +12287,7 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="269" hidden="true" outlineLevel="2">
+    <row r="269" hidden="false" outlineLevel="2">
       <c r="A269" t="s" s="35">
         <v>300</v>
       </c>
@@ -12307,8 +12309,8 @@
       <c r="G269" t="n" s="31">
         <v>46157.0</v>
       </c>
-      <c r="H269" t="n" s="61">
-        <v>46157.0</v>
+      <c r="H269" t="n" s="31">
+        <v>46153.0</v>
       </c>
       <c r="I269" s="7"/>
       <c r="J269" t="n" s="41">
@@ -12326,7 +12328,7 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="270" hidden="true" outlineLevel="2">
+    <row r="270" hidden="false" outlineLevel="2">
       <c r="A270" t="s" s="35">
         <v>300</v>
       </c>
@@ -12348,8 +12350,8 @@
       <c r="G270" t="n" s="31">
         <v>46157.0</v>
       </c>
-      <c r="H270" t="n" s="61">
-        <v>46157.0</v>
+      <c r="H270" t="n" s="31">
+        <v>46153.0</v>
       </c>
       <c r="I270" s="7"/>
       <c r="J270" t="n" s="41">
@@ -12367,7 +12369,7 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="271" hidden="true" outlineLevel="2">
+    <row r="271" hidden="false" outlineLevel="2">
       <c r="A271" t="s" s="35">
         <v>300</v>
       </c>
@@ -12389,8 +12391,8 @@
       <c r="G271" t="n" s="31">
         <v>46157.0</v>
       </c>
-      <c r="H271" t="n" s="61">
-        <v>46157.0</v>
+      <c r="H271" t="n" s="31">
+        <v>46153.0</v>
       </c>
       <c r="I271" s="7"/>
       <c r="J271" t="n" s="41">
@@ -12408,7 +12410,7 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="272" hidden="true" outlineLevel="1">
+    <row r="272" hidden="false" outlineLevel="1">
       <c r="A272" t="s" s="23">
         <v>70</v>
       </c>
@@ -12435,7 +12437,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="273" hidden="true" outlineLevel="2">
+    <row r="273" hidden="false" outlineLevel="2">
       <c r="A273" t="s" s="35">
         <v>301</v>
       </c>
@@ -12458,7 +12460,7 @@
         <v>46175.0</v>
       </c>
       <c r="H273" t="n" s="41">
-        <v>46175.0</v>
+        <v>46171.0</v>
       </c>
       <c r="I273" s="7"/>
       <c r="J273" t="n" s="41">
@@ -12476,7 +12478,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="274" hidden="true" outlineLevel="2">
+    <row r="274" hidden="false" outlineLevel="2">
       <c r="A274" t="s" s="35">
         <v>301</v>
       </c>
@@ -12499,7 +12501,7 @@
         <v>46175.0</v>
       </c>
       <c r="H274" t="n" s="41">
-        <v>46175.0</v>
+        <v>46171.0</v>
       </c>
       <c r="I274" s="7"/>
       <c r="J274" t="n" s="41">
@@ -12517,7 +12519,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="275" hidden="true" outlineLevel="2">
+    <row r="275" hidden="false" outlineLevel="2">
       <c r="A275" t="s" s="35">
         <v>301</v>
       </c>
@@ -12540,7 +12542,7 @@
         <v>46175.0</v>
       </c>
       <c r="H275" t="n" s="41">
-        <v>46175.0</v>
+        <v>46171.0</v>
       </c>
       <c r="I275" s="7"/>
       <c r="J275" t="n" s="41">
@@ -12558,7 +12560,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="276" hidden="true" outlineLevel="2">
+    <row r="276" hidden="false" outlineLevel="2">
       <c r="A276" t="s" s="35">
         <v>301</v>
       </c>
@@ -12581,7 +12583,7 @@
         <v>46175.0</v>
       </c>
       <c r="H276" t="n" s="41">
-        <v>46175.0</v>
+        <v>46171.0</v>
       </c>
       <c r="I276" s="7"/>
       <c r="J276" t="n" s="41">
@@ -12599,7 +12601,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="277" hidden="true" outlineLevel="2">
+    <row r="277" hidden="false" outlineLevel="2">
       <c r="A277" t="s" s="35">
         <v>301</v>
       </c>
@@ -12622,7 +12624,7 @@
         <v>46175.0</v>
       </c>
       <c r="H277" t="n" s="41">
-        <v>46175.0</v>
+        <v>46171.0</v>
       </c>
       <c r="I277" s="7"/>
       <c r="J277" t="n" s="41">
@@ -12640,7 +12642,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="278" hidden="true" outlineLevel="1">
+    <row r="278" hidden="false" outlineLevel="1">
       <c r="A278" t="s" s="23">
         <v>77</v>
       </c>
@@ -12667,7 +12669,7 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="279" hidden="true" outlineLevel="2">
+    <row r="279" hidden="false" outlineLevel="2">
       <c r="A279" t="s" s="35">
         <v>302</v>
       </c>
@@ -12689,8 +12691,8 @@
       <c r="G279" t="n" s="31">
         <v>46192.0</v>
       </c>
-      <c r="H279" t="n" s="61">
-        <v>46192.0</v>
+      <c r="H279" t="n" s="31">
+        <v>46188.0</v>
       </c>
       <c r="I279" s="7"/>
       <c r="J279" t="n" s="41">
@@ -12708,7 +12710,7 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="280" hidden="true" outlineLevel="2">
+    <row r="280" hidden="false" outlineLevel="2">
       <c r="A280" t="s" s="35">
         <v>302</v>
       </c>
@@ -12730,8 +12732,8 @@
       <c r="G280" t="n" s="31">
         <v>46192.0</v>
       </c>
-      <c r="H280" t="n" s="61">
-        <v>46192.0</v>
+      <c r="H280" t="n" s="31">
+        <v>46188.0</v>
       </c>
       <c r="I280" s="7"/>
       <c r="J280" t="n" s="41">
@@ -12749,7 +12751,7 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="281" hidden="true" outlineLevel="2">
+    <row r="281" hidden="false" outlineLevel="2">
       <c r="A281" t="s" s="35">
         <v>302</v>
       </c>
@@ -12771,8 +12773,8 @@
       <c r="G281" t="n" s="31">
         <v>46192.0</v>
       </c>
-      <c r="H281" t="n" s="61">
-        <v>46192.0</v>
+      <c r="H281" t="n" s="31">
+        <v>46188.0</v>
       </c>
       <c r="I281" s="7"/>
       <c r="J281" t="n" s="41">
@@ -12790,7 +12792,7 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="282" hidden="true" outlineLevel="2">
+    <row r="282" hidden="false" outlineLevel="2">
       <c r="A282" t="s" s="35">
         <v>302</v>
       </c>
@@ -12812,8 +12814,8 @@
       <c r="G282" t="n" s="31">
         <v>46192.0</v>
       </c>
-      <c r="H282" t="n" s="61">
-        <v>46192.0</v>
+      <c r="H282" t="n" s="31">
+        <v>46188.0</v>
       </c>
       <c r="I282" s="7"/>
       <c r="J282" t="n" s="41">
@@ -12831,7 +12833,7 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="283" hidden="true" outlineLevel="2">
+    <row r="283" hidden="false" outlineLevel="2">
       <c r="A283" t="s" s="35">
         <v>302</v>
       </c>
@@ -12853,8 +12855,8 @@
       <c r="G283" t="n" s="31">
         <v>46192.0</v>
       </c>
-      <c r="H283" t="n" s="61">
-        <v>46192.0</v>
+      <c r="H283" t="n" s="31">
+        <v>46188.0</v>
       </c>
       <c r="I283" s="7"/>
       <c r="J283" t="n" s="41">
@@ -12872,7 +12874,7 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="284" hidden="true" outlineLevel="1">
+    <row r="284" hidden="false" outlineLevel="1">
       <c r="A284" t="s" s="23">
         <v>84</v>
       </c>
@@ -12899,7 +12901,7 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="285" hidden="true" outlineLevel="2">
+    <row r="285" hidden="false" outlineLevel="2">
       <c r="A285" t="s" s="35">
         <v>303</v>
       </c>
@@ -12922,7 +12924,7 @@
         <v>46206.0</v>
       </c>
       <c r="H285" t="n" s="41">
-        <v>46206.0</v>
+        <v>46202.0</v>
       </c>
       <c r="I285" s="7"/>
       <c r="J285" t="n" s="41">
@@ -12940,7 +12942,7 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="286" hidden="true" outlineLevel="2">
+    <row r="286" hidden="false" outlineLevel="2">
       <c r="A286" t="s" s="35">
         <v>303</v>
       </c>
@@ -12963,7 +12965,7 @@
         <v>46206.0</v>
       </c>
       <c r="H286" t="n" s="41">
-        <v>46206.0</v>
+        <v>46202.0</v>
       </c>
       <c r="I286" s="7"/>
       <c r="J286" t="n" s="41">
@@ -12981,7 +12983,7 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="287" hidden="true" outlineLevel="2">
+    <row r="287" hidden="false" outlineLevel="2">
       <c r="A287" t="s" s="35">
         <v>303</v>
       </c>
@@ -13004,7 +13006,7 @@
         <v>46206.0</v>
       </c>
       <c r="H287" t="n" s="41">
-        <v>46206.0</v>
+        <v>46202.0</v>
       </c>
       <c r="I287" s="7"/>
       <c r="J287" t="n" s="41">
@@ -13022,7 +13024,7 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="288" hidden="true" outlineLevel="2">
+    <row r="288" hidden="false" outlineLevel="2">
       <c r="A288" t="s" s="35">
         <v>303</v>
       </c>
@@ -13045,7 +13047,7 @@
         <v>46206.0</v>
       </c>
       <c r="H288" t="n" s="41">
-        <v>46206.0</v>
+        <v>46202.0</v>
       </c>
       <c r="I288" s="7"/>
       <c r="J288" t="n" s="41">
@@ -13063,7 +13065,7 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="289" hidden="true" outlineLevel="2">
+    <row r="289" hidden="false" outlineLevel="2">
       <c r="A289" t="s" s="35">
         <v>303</v>
       </c>
@@ -13086,7 +13088,7 @@
         <v>46206.0</v>
       </c>
       <c r="H289" t="n" s="41">
-        <v>46206.0</v>
+        <v>46202.0</v>
       </c>
       <c r="I289" s="7"/>
       <c r="J289" t="n" s="41">
@@ -13104,7 +13106,7 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="290" hidden="true" outlineLevel="1">
+    <row r="290" hidden="false" outlineLevel="1">
       <c r="A290" t="s" s="23">
         <v>89</v>
       </c>
@@ -13131,7 +13133,7 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="291" hidden="true" outlineLevel="2">
+    <row r="291" hidden="false" outlineLevel="2">
       <c r="A291" t="s" s="35">
         <v>304</v>
       </c>
@@ -13153,8 +13155,8 @@
       <c r="G291" t="n" s="31">
         <v>46220.0</v>
       </c>
-      <c r="H291" t="n" s="61">
-        <v>46220.0</v>
+      <c r="H291" t="n" s="31">
+        <v>46216.0</v>
       </c>
       <c r="I291" s="7"/>
       <c r="J291" t="n" s="41">
@@ -13172,7 +13174,7 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="292" hidden="true" outlineLevel="2">
+    <row r="292" hidden="false" outlineLevel="2">
       <c r="A292" t="s" s="35">
         <v>304</v>
       </c>
@@ -13194,8 +13196,8 @@
       <c r="G292" t="n" s="31">
         <v>46220.0</v>
       </c>
-      <c r="H292" t="n" s="61">
-        <v>46220.0</v>
+      <c r="H292" t="n" s="31">
+        <v>46216.0</v>
       </c>
       <c r="I292" s="7"/>
       <c r="J292" t="n" s="41">
@@ -13213,7 +13215,7 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="293" hidden="true" outlineLevel="2">
+    <row r="293" hidden="false" outlineLevel="2">
       <c r="A293" t="s" s="35">
         <v>304</v>
       </c>
@@ -13235,8 +13237,8 @@
       <c r="G293" t="n" s="31">
         <v>46220.0</v>
       </c>
-      <c r="H293" t="n" s="61">
-        <v>46220.0</v>
+      <c r="H293" t="n" s="31">
+        <v>46216.0</v>
       </c>
       <c r="I293" s="7"/>
       <c r="J293" t="n" s="41">
@@ -13254,7 +13256,7 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="294" hidden="true" outlineLevel="2">
+    <row r="294" hidden="false" outlineLevel="2">
       <c r="A294" t="s" s="35">
         <v>304</v>
       </c>
@@ -13276,8 +13278,8 @@
       <c r="G294" t="n" s="31">
         <v>46220.0</v>
       </c>
-      <c r="H294" t="n" s="61">
-        <v>46220.0</v>
+      <c r="H294" t="n" s="31">
+        <v>46216.0</v>
       </c>
       <c r="I294" s="7"/>
       <c r="J294" t="n" s="41">
@@ -13295,7 +13297,7 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="295" hidden="true" outlineLevel="2">
+    <row r="295" hidden="false" outlineLevel="2">
       <c r="A295" t="s" s="35">
         <v>304</v>
       </c>
@@ -13317,8 +13319,8 @@
       <c r="G295" t="n" s="31">
         <v>46220.0</v>
       </c>
-      <c r="H295" t="n" s="61">
-        <v>46220.0</v>
+      <c r="H295" t="n" s="31">
+        <v>46216.0</v>
       </c>
       <c r="I295" s="7"/>
       <c r="J295" t="n" s="41">
@@ -13336,7 +13338,7 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="296" hidden="true" outlineLevel="1">
+    <row r="296" hidden="false" outlineLevel="1">
       <c r="A296" t="s" s="23">
         <v>96</v>
       </c>
@@ -13363,7 +13365,7 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="297" hidden="true" outlineLevel="2">
+    <row r="297" hidden="false" outlineLevel="2">
       <c r="A297" t="s" s="35">
         <v>305</v>
       </c>
@@ -13386,7 +13388,7 @@
         <v>46234.0</v>
       </c>
       <c r="H297" t="n" s="41">
-        <v>46234.0</v>
+        <v>46230.0</v>
       </c>
       <c r="I297" s="7"/>
       <c r="J297" t="n" s="41">
@@ -13404,7 +13406,7 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="298" hidden="true" outlineLevel="2">
+    <row r="298" hidden="false" outlineLevel="2">
       <c r="A298" t="s" s="35">
         <v>305</v>
       </c>
@@ -13427,7 +13429,7 @@
         <v>46234.0</v>
       </c>
       <c r="H298" t="n" s="41">
-        <v>46234.0</v>
+        <v>46230.0</v>
       </c>
       <c r="I298" s="7"/>
       <c r="J298" t="n" s="41">
@@ -13445,7 +13447,7 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="299" hidden="true" outlineLevel="2">
+    <row r="299" hidden="false" outlineLevel="2">
       <c r="A299" t="s" s="35">
         <v>305</v>
       </c>
@@ -13468,7 +13470,7 @@
         <v>46234.0</v>
       </c>
       <c r="H299" t="n" s="41">
-        <v>46234.0</v>
+        <v>46230.0</v>
       </c>
       <c r="I299" s="7"/>
       <c r="J299" t="n" s="41">
@@ -13486,7 +13488,7 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="300" hidden="true" outlineLevel="2">
+    <row r="300" hidden="false" outlineLevel="2">
       <c r="A300" t="s" s="35">
         <v>305</v>
       </c>
@@ -13509,7 +13511,7 @@
         <v>46234.0</v>
       </c>
       <c r="H300" t="n" s="41">
-        <v>46234.0</v>
+        <v>46230.0</v>
       </c>
       <c r="I300" s="7"/>
       <c r="J300" t="n" s="41">
@@ -13527,7 +13529,7 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="301" hidden="true" outlineLevel="2">
+    <row r="301" hidden="false" outlineLevel="2">
       <c r="A301" t="s" s="35">
         <v>305</v>
       </c>
@@ -13550,7 +13552,7 @@
         <v>46234.0</v>
       </c>
       <c r="H301" t="n" s="41">
-        <v>46234.0</v>
+        <v>46230.0</v>
       </c>
       <c r="I301" s="7"/>
       <c r="J301" t="n" s="41">
@@ -13568,7 +13570,7 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="302" hidden="true" outlineLevel="1">
+    <row r="302" hidden="false" outlineLevel="1">
       <c r="A302" t="s" s="23">
         <v>103</v>
       </c>
@@ -13595,7 +13597,7 @@
         <v>46412.0</v>
       </c>
     </row>
-    <row r="303" hidden="true" outlineLevel="2">
+    <row r="303" hidden="false" outlineLevel="2">
       <c r="A303" t="s" s="35">
         <v>306</v>
       </c>
@@ -13617,8 +13619,8 @@
       <c r="G303" t="n" s="31">
         <v>46248.0</v>
       </c>
-      <c r="H303" t="n" s="61">
-        <v>46248.0</v>
+      <c r="H303" t="n" s="31">
+        <v>46244.0</v>
       </c>
       <c r="I303" s="7"/>
       <c r="J303" t="n" s="41">
@@ -13636,7 +13638,7 @@
         <v>46412.0</v>
       </c>
     </row>
-    <row r="304" hidden="true" outlineLevel="2">
+    <row r="304" hidden="false" outlineLevel="2">
       <c r="A304" t="s" s="35">
         <v>306</v>
       </c>
@@ -13658,8 +13660,8 @@
       <c r="G304" t="n" s="31">
         <v>46248.0</v>
       </c>
-      <c r="H304" t="n" s="61">
-        <v>46248.0</v>
+      <c r="H304" t="n" s="31">
+        <v>46244.0</v>
       </c>
       <c r="I304" s="7"/>
       <c r="J304" t="n" s="41">
@@ -13677,7 +13679,7 @@
         <v>46412.0</v>
       </c>
     </row>
-    <row r="305" hidden="true" outlineLevel="2">
+    <row r="305" hidden="false" outlineLevel="2">
       <c r="A305" t="s" s="35">
         <v>306</v>
       </c>
@@ -13699,8 +13701,8 @@
       <c r="G305" t="n" s="31">
         <v>46248.0</v>
       </c>
-      <c r="H305" t="n" s="61">
-        <v>46248.0</v>
+      <c r="H305" t="n" s="31">
+        <v>46244.0</v>
       </c>
       <c r="I305" s="7"/>
       <c r="J305" t="n" s="41">
@@ -13718,7 +13720,7 @@
         <v>46412.0</v>
       </c>
     </row>
-    <row r="306" hidden="true" outlineLevel="2">
+    <row r="306" hidden="false" outlineLevel="2">
       <c r="A306" t="s" s="35">
         <v>306</v>
       </c>
@@ -13740,8 +13742,8 @@
       <c r="G306" t="n" s="31">
         <v>46248.0</v>
       </c>
-      <c r="H306" t="n" s="61">
-        <v>46248.0</v>
+      <c r="H306" t="n" s="31">
+        <v>46244.0</v>
       </c>
       <c r="I306" s="7"/>
       <c r="J306" t="n" s="41">
@@ -13759,7 +13761,7 @@
         <v>46412.0</v>
       </c>
     </row>
-    <row r="307" hidden="true" outlineLevel="2">
+    <row r="307" hidden="false" outlineLevel="2">
       <c r="A307" t="s" s="35">
         <v>306</v>
       </c>
@@ -13781,8 +13783,8 @@
       <c r="G307" t="n" s="31">
         <v>46248.0</v>
       </c>
-      <c r="H307" t="n" s="61">
-        <v>46248.0</v>
+      <c r="H307" t="n" s="31">
+        <v>46244.0</v>
       </c>
       <c r="I307" s="7"/>
       <c r="J307" t="n" s="41">
@@ -13882,7 +13884,7 @@
         <v>46027.0</v>
       </c>
       <c r="H311" t="n" s="41">
-        <v>46027.0</v>
+        <v>46066.0</v>
       </c>
       <c r="I311" s="7"/>
       <c r="J311" t="n" s="41">
@@ -13925,7 +13927,7 @@
         <v>46083.0</v>
       </c>
       <c r="H312" t="n" s="31">
-        <v>46083.0</v>
+        <v>46108.0</v>
       </c>
       <c r="I312" s="7"/>
       <c r="J312" t="n" s="31">
@@ -13968,7 +13970,7 @@
         <v>46111.0</v>
       </c>
       <c r="H313" t="n" s="41">
-        <v>46111.0</v>
+        <v>46115.0</v>
       </c>
       <c r="I313" s="7"/>
       <c r="J313" t="n" s="41">
@@ -14011,7 +14013,7 @@
         <v>46129.0</v>
       </c>
       <c r="H314" t="n" s="31">
-        <v>46129.0</v>
+        <v>46125.0</v>
       </c>
       <c r="I314" s="7"/>
       <c r="J314" t="n" s="31">
@@ -14054,7 +14056,7 @@
         <v>46143.0</v>
       </c>
       <c r="H315" t="n" s="41">
-        <v>46143.0</v>
+        <v>46139.0</v>
       </c>
       <c r="I315" s="7"/>
       <c r="J315" t="n" s="41">
@@ -14097,7 +14099,7 @@
         <v>46157.0</v>
       </c>
       <c r="H316" t="n" s="31">
-        <v>46157.0</v>
+        <v>46153.0</v>
       </c>
       <c r="I316" s="7"/>
       <c r="J316" t="n" s="31">
@@ -14140,7 +14142,7 @@
         <v>46175.0</v>
       </c>
       <c r="H317" t="n" s="41">
-        <v>46175.0</v>
+        <v>46171.0</v>
       </c>
       <c r="I317" s="7"/>
       <c r="J317" t="n" s="41">
@@ -14183,7 +14185,7 @@
         <v>46192.0</v>
       </c>
       <c r="H318" t="n" s="31">
-        <v>46192.0</v>
+        <v>46188.0</v>
       </c>
       <c r="I318" s="7"/>
       <c r="J318" t="n" s="31">
@@ -14226,7 +14228,7 @@
         <v>46206.0</v>
       </c>
       <c r="H319" t="n" s="41">
-        <v>46206.0</v>
+        <v>46202.0</v>
       </c>
       <c r="I319" s="7"/>
       <c r="J319" t="n" s="41">
@@ -14269,7 +14271,7 @@
         <v>46220.0</v>
       </c>
       <c r="H320" t="n" s="31">
-        <v>46220.0</v>
+        <v>46216.0</v>
       </c>
       <c r="I320" s="7"/>
       <c r="J320" t="n" s="31">
@@ -14312,7 +14314,7 @@
         <v>46234.0</v>
       </c>
       <c r="H321" t="n" s="41">
-        <v>46234.0</v>
+        <v>46230.0</v>
       </c>
       <c r="I321" s="7"/>
       <c r="J321" t="n" s="41">
@@ -14355,7 +14357,7 @@
         <v>46248.0</v>
       </c>
       <c r="H322" t="n" s="31">
-        <v>46248.0</v>
+        <v>46244.0</v>
       </c>
       <c r="I322" s="7"/>
       <c r="J322" t="n" s="31">
@@ -14444,7 +14446,7 @@
         <v>327</v>
       </c>
       <c r="B1" t="n" s="86">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="2">
@@ -14860,7 +14862,7 @@
         <v>379</v>
       </c>
       <c r="B53" t="n" s="86">
-        <v>35.0</v>
+        <v>-14.0</v>
       </c>
     </row>
     <row r="54">
@@ -14868,7 +14870,7 @@
         <v>380</v>
       </c>
       <c r="B54" t="n" s="86">
-        <v>56.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="55">
@@ -14876,7 +14878,7 @@
         <v>381</v>
       </c>
       <c r="B55" t="n" s="86">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="56">
@@ -14884,7 +14886,7 @@
         <v>382</v>
       </c>
       <c r="B56" t="n" s="86">
-        <v>66.0</v>
+        <v>77.0</v>
       </c>
     </row>
     <row r="57">
@@ -14892,7 +14894,7 @@
         <v>383</v>
       </c>
       <c r="B57" t="n" s="86">
-        <v>80.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="58">
@@ -14900,7 +14902,7 @@
         <v>384</v>
       </c>
       <c r="B58" t="n" s="86">
-        <v>94.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="59">
@@ -14908,7 +14910,7 @@
         <v>385</v>
       </c>
       <c r="B59" t="n" s="86">
-        <v>104.0</v>
+        <v>119.0</v>
       </c>
     </row>
     <row r="60">
@@ -14916,7 +14918,7 @@
         <v>386</v>
       </c>
       <c r="B60" t="n" s="86">
-        <v>115.0</v>
+        <v>133.0</v>
       </c>
     </row>
     <row r="61">
@@ -14924,7 +14926,7 @@
         <v>387</v>
       </c>
       <c r="B61" t="n" s="86">
-        <v>129.0</v>
+        <v>147.0</v>
       </c>
     </row>
     <row r="62">
@@ -14932,7 +14934,7 @@
         <v>388</v>
       </c>
       <c r="B62" t="n" s="86">
-        <v>143.0</v>
+        <v>161.0</v>
       </c>
     </row>
     <row r="63">
@@ -14940,7 +14942,7 @@
         <v>389</v>
       </c>
       <c r="B63" t="n" s="86">
-        <v>157.0</v>
+        <v>175.0</v>
       </c>
     </row>
     <row r="64">
@@ -14948,7 +14950,7 @@
         <v>390</v>
       </c>
       <c r="B64" t="n" s="86">
-        <v>171.0</v>
+        <v>189.0</v>
       </c>
     </row>
     <row r="65">

--- a/03. CMH120 OFCI Log REV2.0.xlsx
+++ b/03. CMH120 OFCI Log REV2.0.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6126" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6127" uniqueCount="464">
   <si>
     <t/>
   </si>
@@ -808,7 +808,7 @@
     <t>trevor_hanks@w-industries.com</t>
   </si>
   <si>
-    <t>OSA Delivery - 12/8/2025</t>
+    <t>OSA Delivery - 12/22/2025</t>
   </si>
   <si>
     <t>ROMP 02 TETRIS SWITCHGEAR</t>
@@ -878,6 +878,9 @@
   </si>
   <si>
     <t>LV PANELS</t>
+  </si>
+  <si>
+    <t>OSA Delivery - 1/19/2026</t>
   </si>
   <si>
     <t>ROMP 01 LV PANELS</t>
@@ -4757,7 +4760,7 @@
       <c r="P70" s="15"/>
       <c r="Q70" s="15"/>
     </row>
-    <row r="71" hidden="true" outlineLevel="1">
+    <row r="71" hidden="false" outlineLevel="1">
       <c r="A71" t="s" s="45">
         <v>111</v>
       </c>
@@ -4804,7 +4807,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="72" hidden="true" outlineLevel="1">
+    <row r="72" hidden="false" outlineLevel="1">
       <c r="A72" t="s" s="45">
         <v>111</v>
       </c>
@@ -7077,7 +7080,7 @@
       <c r="P132" s="15"/>
       <c r="Q132" s="15"/>
     </row>
-    <row r="133" hidden="false" outlineLevel="1">
+    <row r="133" hidden="true" outlineLevel="1">
       <c r="A133" s="21"/>
       <c r="B133" s="5"/>
       <c r="C133" s="7"/>
@@ -7096,7 +7099,7 @@
       <c r="P133" s="5"/>
       <c r="Q133" s="5"/>
     </row>
-    <row r="134" hidden="false" outlineLevel="1">
+    <row r="134" hidden="true" outlineLevel="1">
       <c r="A134" t="s" s="23">
         <v>19</v>
       </c>
@@ -7119,7 +7122,7 @@
         <v>46027.0</v>
       </c>
       <c r="H134" t="n" s="31">
-        <v>46027.0</v>
+        <v>46028.0</v>
       </c>
       <c r="I134" s="27"/>
       <c r="J134" s="27"/>
@@ -7135,7 +7138,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="135" hidden="false" outlineLevel="2">
+    <row r="135" hidden="true" outlineLevel="2">
       <c r="A135" t="s" s="35">
         <v>169</v>
       </c>
@@ -7176,7 +7179,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="136" hidden="false" outlineLevel="2">
+    <row r="136" hidden="true" outlineLevel="2">
       <c r="A136" t="s" s="35">
         <v>169</v>
       </c>
@@ -7217,7 +7220,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="137" hidden="false" outlineLevel="2">
+    <row r="137" hidden="true" outlineLevel="2">
       <c r="A137" t="s" s="35">
         <v>169</v>
       </c>
@@ -7258,7 +7261,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="138" hidden="false" outlineLevel="2">
+    <row r="138" hidden="true" outlineLevel="2">
       <c r="A138" t="s" s="35">
         <v>169</v>
       </c>
@@ -7299,7 +7302,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="139" hidden="false" outlineLevel="2">
+    <row r="139" hidden="true" outlineLevel="2">
       <c r="A139" t="s" s="35">
         <v>169</v>
       </c>
@@ -7340,7 +7343,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="140" hidden="false" outlineLevel="2">
+    <row r="140" hidden="true" outlineLevel="2">
       <c r="A140" t="s" s="35">
         <v>169</v>
       </c>
@@ -10422,7 +10425,7 @@
       <c r="P219" s="81"/>
       <c r="Q219" s="81"/>
     </row>
-    <row r="220" hidden="false" outlineLevel="1">
+    <row r="220" hidden="true" outlineLevel="1">
       <c r="A220" s="21"/>
       <c r="B220" s="5"/>
       <c r="C220" s="7"/>
@@ -10441,7 +10444,7 @@
       <c r="P220" s="5"/>
       <c r="Q220" s="5"/>
     </row>
-    <row r="221" hidden="false" outlineLevel="1">
+    <row r="221" hidden="true" outlineLevel="1">
       <c r="A221" t="s" s="21">
         <v>261</v>
       </c>
@@ -10484,7 +10487,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="222" hidden="false" outlineLevel="1">
+    <row r="222" hidden="true" outlineLevel="1">
       <c r="A222" t="s" s="23">
         <v>265</v>
       </c>
@@ -10527,7 +10530,7 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="223" hidden="false" outlineLevel="1">
+    <row r="223" hidden="true" outlineLevel="1">
       <c r="A223" t="s" s="21">
         <v>268</v>
       </c>
@@ -10570,7 +10573,7 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="224" hidden="false" outlineLevel="1">
+    <row r="224" hidden="true" outlineLevel="1">
       <c r="A224" t="s" s="23">
         <v>269</v>
       </c>
@@ -10613,7 +10616,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="225" hidden="false" outlineLevel="1">
+    <row r="225" hidden="true" outlineLevel="1">
       <c r="A225" t="s" s="21">
         <v>271</v>
       </c>
@@ -10656,7 +10659,7 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="226" hidden="false" outlineLevel="1">
+    <row r="226" hidden="true" outlineLevel="1">
       <c r="A226" t="s" s="23">
         <v>273</v>
       </c>
@@ -10699,7 +10702,7 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="227" hidden="false" outlineLevel="1">
+    <row r="227" hidden="true" outlineLevel="1">
       <c r="A227" t="s" s="21">
         <v>275</v>
       </c>
@@ -10742,7 +10745,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="228" hidden="false" outlineLevel="1">
+    <row r="228" hidden="true" outlineLevel="1">
       <c r="A228" t="s" s="23">
         <v>277</v>
       </c>
@@ -10785,7 +10788,7 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="229" hidden="false" outlineLevel="1">
+    <row r="229" hidden="true" outlineLevel="1">
       <c r="A229" t="s" s="21">
         <v>279</v>
       </c>
@@ -10828,7 +10831,7 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="230" hidden="false" outlineLevel="1">
+    <row r="230" hidden="true" outlineLevel="1">
       <c r="A230" t="s" s="23">
         <v>281</v>
       </c>
@@ -10871,7 +10874,7 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="231" hidden="false" outlineLevel="1">
+    <row r="231" hidden="true" outlineLevel="1">
       <c r="A231" t="s" s="21">
         <v>283</v>
       </c>
@@ -10914,7 +10917,7 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="232" hidden="false" outlineLevel="1">
+    <row r="232" hidden="true" outlineLevel="1">
       <c r="A232" t="s" s="23">
         <v>285</v>
       </c>
@@ -10997,7 +11000,7 @@
       <c r="P234" s="81"/>
       <c r="Q234" s="81"/>
     </row>
-    <row r="235" hidden="false" outlineLevel="1">
+    <row r="235" hidden="true" outlineLevel="1">
       <c r="A235" s="21"/>
       <c r="B235" s="5"/>
       <c r="C235" s="7"/>
@@ -11016,7 +11019,7 @@
       <c r="P235" s="5"/>
       <c r="Q235" s="5"/>
     </row>
-    <row r="236" hidden="false" outlineLevel="1">
+    <row r="236" hidden="true" outlineLevel="1">
       <c r="A236" t="s" s="23">
         <v>19</v>
       </c>
@@ -11036,7 +11039,9 @@
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c r="M236" s="7"/>
-      <c r="N236" s="11"/>
+      <c r="N236" t="s" s="11">
+        <v>288</v>
+      </c>
       <c r="O236" t="s" s="27">
         <v>20</v>
       </c>
@@ -11045,24 +11050,24 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="237" hidden="false" outlineLevel="2">
+    <row r="237" hidden="true" outlineLevel="2">
       <c r="A237" t="s" s="35">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B237" t="s" s="5">
         <v>22</v>
       </c>
       <c r="C237" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D237" t="s" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E237" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F237" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G237" t="n" s="41">
         <v>46027.0</v>
@@ -11086,24 +11091,24 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="238" hidden="false" outlineLevel="2">
+    <row r="238" hidden="true" outlineLevel="2">
       <c r="A238" t="s" s="35">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B238" t="s" s="5">
         <v>22</v>
       </c>
       <c r="C238" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D238" t="s" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E238" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F238" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G238" t="n" s="41">
         <v>46027.0</v>
@@ -11127,24 +11132,24 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="239" hidden="false" outlineLevel="2">
+    <row r="239" hidden="true" outlineLevel="2">
       <c r="A239" t="s" s="35">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B239" t="s" s="5">
         <v>22</v>
       </c>
       <c r="C239" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D239" t="s" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E239" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F239" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G239" t="n" s="41">
         <v>46027.0</v>
@@ -11168,24 +11173,24 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="240" hidden="false" outlineLevel="2">
+    <row r="240" hidden="true" outlineLevel="2">
       <c r="A240" t="s" s="35">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B240" t="s" s="5">
         <v>22</v>
       </c>
       <c r="C240" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D240" t="s" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E240" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F240" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G240" t="n" s="41">
         <v>46027.0</v>
@@ -11209,24 +11214,24 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="241" hidden="false" outlineLevel="2">
+    <row r="241" hidden="true" outlineLevel="2">
       <c r="A241" t="s" s="35">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B241" t="s" s="5">
         <v>22</v>
       </c>
       <c r="C241" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D241" t="s" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E241" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F241" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G241" t="n" s="41">
         <v>46027.0</v>
@@ -11250,7 +11255,7 @@
         <v>46055.0</v>
       </c>
     </row>
-    <row r="242" hidden="false" outlineLevel="1">
+    <row r="242" hidden="true" outlineLevel="1">
       <c r="A242" t="s" s="23">
         <v>35</v>
       </c>
@@ -11277,24 +11282,24 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="243" hidden="false" outlineLevel="2">
+    <row r="243" hidden="true" outlineLevel="2">
       <c r="A243" t="s" s="35">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B243" t="s" s="5">
         <v>37</v>
       </c>
       <c r="C243" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D243" t="s" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E243" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F243" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G243" t="n" s="31">
         <v>46097.0</v>
@@ -11318,24 +11323,24 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="244" hidden="false" outlineLevel="2">
+    <row r="244" hidden="true" outlineLevel="2">
       <c r="A244" t="s" s="35">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B244" t="s" s="5">
         <v>37</v>
       </c>
       <c r="C244" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D244" t="s" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E244" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F244" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G244" t="n" s="31">
         <v>46097.0</v>
@@ -11359,24 +11364,24 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="245" hidden="false" outlineLevel="2">
+    <row r="245" hidden="true" outlineLevel="2">
       <c r="A245" t="s" s="35">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B245" t="s" s="5">
         <v>37</v>
       </c>
       <c r="C245" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D245" t="s" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E245" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F245" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G245" t="n" s="31">
         <v>46097.0</v>
@@ -11400,24 +11405,24 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="246" hidden="false" outlineLevel="2">
+    <row r="246" hidden="true" outlineLevel="2">
       <c r="A246" t="s" s="35">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B246" t="s" s="5">
         <v>37</v>
       </c>
       <c r="C246" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D246" t="s" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E246" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F246" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G246" t="n" s="31">
         <v>46097.0</v>
@@ -11441,24 +11446,24 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="247" hidden="false" outlineLevel="2">
+    <row r="247" hidden="true" outlineLevel="2">
       <c r="A247" t="s" s="35">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B247" t="s" s="5">
         <v>37</v>
       </c>
       <c r="C247" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D247" t="s" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E247" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F247" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G247" t="n" s="31">
         <v>46097.0</v>
@@ -11482,7 +11487,7 @@
         <v>46132.0</v>
       </c>
     </row>
-    <row r="248" hidden="false" outlineLevel="1">
+    <row r="248" hidden="true" outlineLevel="1">
       <c r="A248" t="s" s="23">
         <v>42</v>
       </c>
@@ -11509,24 +11514,24 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="249" hidden="false" outlineLevel="2">
+    <row r="249" hidden="true" outlineLevel="2">
       <c r="A249" t="s" s="35">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B249" t="s" s="5">
         <v>44</v>
       </c>
       <c r="C249" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D249" t="s" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E249" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F249" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G249" t="n" s="41">
         <v>46111.0</v>
@@ -11550,24 +11555,24 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="250" hidden="false" outlineLevel="2">
+    <row r="250" hidden="true" outlineLevel="2">
       <c r="A250" t="s" s="35">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B250" t="s" s="5">
         <v>44</v>
       </c>
       <c r="C250" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D250" t="s" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E250" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F250" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G250" t="n" s="41">
         <v>46111.0</v>
@@ -11591,24 +11596,24 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="251" hidden="false" outlineLevel="2">
+    <row r="251" hidden="true" outlineLevel="2">
       <c r="A251" t="s" s="35">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B251" t="s" s="5">
         <v>44</v>
       </c>
       <c r="C251" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D251" t="s" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E251" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F251" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G251" t="n" s="41">
         <v>46111.0</v>
@@ -11632,24 +11637,24 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="252" hidden="false" outlineLevel="2">
+    <row r="252" hidden="true" outlineLevel="2">
       <c r="A252" t="s" s="35">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B252" t="s" s="5">
         <v>44</v>
       </c>
       <c r="C252" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D252" t="s" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E252" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F252" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G252" t="n" s="41">
         <v>46111.0</v>
@@ -11673,24 +11678,24 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="253" hidden="false" outlineLevel="2">
+    <row r="253" hidden="true" outlineLevel="2">
       <c r="A253" t="s" s="35">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B253" t="s" s="5">
         <v>44</v>
       </c>
       <c r="C253" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D253" t="s" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E253" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F253" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G253" t="n" s="41">
         <v>46111.0</v>
@@ -11714,7 +11719,7 @@
         <v>46160.0</v>
       </c>
     </row>
-    <row r="254" hidden="false" outlineLevel="1">
+    <row r="254" hidden="true" outlineLevel="1">
       <c r="A254" t="s" s="23">
         <v>49</v>
       </c>
@@ -11741,24 +11746,24 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="255" hidden="false" outlineLevel="2">
+    <row r="255" hidden="true" outlineLevel="2">
       <c r="A255" t="s" s="35">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B255" t="s" s="37">
         <v>51</v>
       </c>
       <c r="C255" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D255" t="s" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E255" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F255" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G255" t="n" s="31">
         <v>46129.0</v>
@@ -11782,24 +11787,24 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="256" hidden="false" outlineLevel="2">
+    <row r="256" hidden="true" outlineLevel="2">
       <c r="A256" t="s" s="35">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B256" t="s" s="37">
         <v>51</v>
       </c>
       <c r="C256" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D256" t="s" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E256" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F256" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G256" t="n" s="31">
         <v>46129.0</v>
@@ -11823,24 +11828,24 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="257" hidden="false" outlineLevel="2">
+    <row r="257" hidden="true" outlineLevel="2">
       <c r="A257" t="s" s="35">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B257" t="s" s="37">
         <v>51</v>
       </c>
       <c r="C257" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D257" t="s" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E257" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F257" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G257" t="n" s="31">
         <v>46129.0</v>
@@ -11864,24 +11869,24 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="258" hidden="false" outlineLevel="2">
+    <row r="258" hidden="true" outlineLevel="2">
       <c r="A258" t="s" s="35">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B258" t="s" s="37">
         <v>51</v>
       </c>
       <c r="C258" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D258" t="s" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E258" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F258" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G258" t="n" s="31">
         <v>46129.0</v>
@@ -11905,24 +11910,24 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="259" hidden="false" outlineLevel="2">
+    <row r="259" hidden="true" outlineLevel="2">
       <c r="A259" t="s" s="35">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B259" t="s" s="37">
         <v>51</v>
       </c>
       <c r="C259" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D259" t="s" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E259" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F259" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G259" t="n" s="31">
         <v>46129.0</v>
@@ -11946,7 +11951,7 @@
         <v>46188.0</v>
       </c>
     </row>
-    <row r="260" hidden="false" outlineLevel="1">
+    <row r="260" hidden="true" outlineLevel="1">
       <c r="A260" t="s" s="23">
         <v>56</v>
       </c>
@@ -11973,24 +11978,24 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="261" hidden="false" outlineLevel="2">
+    <row r="261" hidden="true" outlineLevel="2">
       <c r="A261" t="s" s="35">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B261" t="s" s="5">
         <v>58</v>
       </c>
       <c r="C261" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D261" t="s" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E261" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F261" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G261" t="n" s="41">
         <v>46143.0</v>
@@ -12014,24 +12019,24 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="262" hidden="false" outlineLevel="2">
+    <row r="262" hidden="true" outlineLevel="2">
       <c r="A262" t="s" s="35">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B262" t="s" s="5">
         <v>58</v>
       </c>
       <c r="C262" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D262" t="s" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E262" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F262" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G262" t="n" s="41">
         <v>46143.0</v>
@@ -12055,24 +12060,24 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="263" hidden="false" outlineLevel="2">
+    <row r="263" hidden="true" outlineLevel="2">
       <c r="A263" t="s" s="35">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B263" t="s" s="5">
         <v>58</v>
       </c>
       <c r="C263" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D263" t="s" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E263" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F263" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G263" t="n" s="41">
         <v>46143.0</v>
@@ -12096,24 +12101,24 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="264" hidden="false" outlineLevel="2">
+    <row r="264" hidden="true" outlineLevel="2">
       <c r="A264" t="s" s="35">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B264" t="s" s="5">
         <v>58</v>
       </c>
       <c r="C264" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D264" t="s" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E264" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F264" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G264" t="n" s="41">
         <v>46143.0</v>
@@ -12137,24 +12142,24 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="265" hidden="false" outlineLevel="2">
+    <row r="265" hidden="true" outlineLevel="2">
       <c r="A265" t="s" s="35">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B265" t="s" s="5">
         <v>58</v>
       </c>
       <c r="C265" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D265" t="s" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E265" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F265" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G265" t="n" s="41">
         <v>46143.0</v>
@@ -12178,7 +12183,7 @@
         <v>46216.0</v>
       </c>
     </row>
-    <row r="266" hidden="false" outlineLevel="1">
+    <row r="266" hidden="true" outlineLevel="1">
       <c r="A266" t="s" s="23">
         <v>63</v>
       </c>
@@ -12205,24 +12210,24 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="267" hidden="false" outlineLevel="2">
+    <row r="267" hidden="true" outlineLevel="2">
       <c r="A267" t="s" s="35">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B267" t="s" s="5">
         <v>65</v>
       </c>
       <c r="C267" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D267" t="s" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E267" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F267" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G267" t="n" s="31">
         <v>46157.0</v>
@@ -12246,24 +12251,24 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="268" hidden="false" outlineLevel="2">
+    <row r="268" hidden="true" outlineLevel="2">
       <c r="A268" t="s" s="35">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B268" t="s" s="5">
         <v>65</v>
       </c>
       <c r="C268" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D268" t="s" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E268" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F268" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G268" t="n" s="31">
         <v>46157.0</v>
@@ -12287,24 +12292,24 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="269" hidden="false" outlineLevel="2">
+    <row r="269" hidden="true" outlineLevel="2">
       <c r="A269" t="s" s="35">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B269" t="s" s="5">
         <v>65</v>
       </c>
       <c r="C269" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D269" t="s" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E269" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F269" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G269" t="n" s="31">
         <v>46157.0</v>
@@ -12328,24 +12333,24 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="270" hidden="false" outlineLevel="2">
+    <row r="270" hidden="true" outlineLevel="2">
       <c r="A270" t="s" s="35">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B270" t="s" s="5">
         <v>65</v>
       </c>
       <c r="C270" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D270" t="s" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E270" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F270" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G270" t="n" s="31">
         <v>46157.0</v>
@@ -12369,24 +12374,24 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="271" hidden="false" outlineLevel="2">
+    <row r="271" hidden="true" outlineLevel="2">
       <c r="A271" t="s" s="35">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B271" t="s" s="5">
         <v>65</v>
       </c>
       <c r="C271" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D271" t="s" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E271" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F271" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G271" t="n" s="31">
         <v>46157.0</v>
@@ -12410,7 +12415,7 @@
         <v>46244.0</v>
       </c>
     </row>
-    <row r="272" hidden="false" outlineLevel="1">
+    <row r="272" hidden="true" outlineLevel="1">
       <c r="A272" t="s" s="23">
         <v>70</v>
       </c>
@@ -12437,24 +12442,24 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="273" hidden="false" outlineLevel="2">
+    <row r="273" hidden="true" outlineLevel="2">
       <c r="A273" t="s" s="35">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B273" t="s" s="5">
         <v>72</v>
       </c>
       <c r="C273" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D273" t="s" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E273" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F273" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G273" t="n" s="41">
         <v>46175.0</v>
@@ -12478,24 +12483,24 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="274" hidden="false" outlineLevel="2">
+    <row r="274" hidden="true" outlineLevel="2">
       <c r="A274" t="s" s="35">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B274" t="s" s="5">
         <v>72</v>
       </c>
       <c r="C274" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D274" t="s" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E274" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F274" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G274" t="n" s="41">
         <v>46175.0</v>
@@ -12519,24 +12524,24 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="275" hidden="false" outlineLevel="2">
+    <row r="275" hidden="true" outlineLevel="2">
       <c r="A275" t="s" s="35">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B275" t="s" s="5">
         <v>72</v>
       </c>
       <c r="C275" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D275" t="s" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E275" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F275" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G275" t="n" s="41">
         <v>46175.0</v>
@@ -12560,24 +12565,24 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="276" hidden="false" outlineLevel="2">
+    <row r="276" hidden="true" outlineLevel="2">
       <c r="A276" t="s" s="35">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B276" t="s" s="5">
         <v>72</v>
       </c>
       <c r="C276" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D276" t="s" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E276" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F276" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G276" t="n" s="41">
         <v>46175.0</v>
@@ -12601,24 +12606,24 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="277" hidden="false" outlineLevel="2">
+    <row r="277" hidden="true" outlineLevel="2">
       <c r="A277" t="s" s="35">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B277" t="s" s="5">
         <v>72</v>
       </c>
       <c r="C277" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D277" t="s" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E277" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F277" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G277" t="n" s="41">
         <v>46175.0</v>
@@ -12642,7 +12647,7 @@
         <v>46272.0</v>
       </c>
     </row>
-    <row r="278" hidden="false" outlineLevel="1">
+    <row r="278" hidden="true" outlineLevel="1">
       <c r="A278" t="s" s="23">
         <v>77</v>
       </c>
@@ -12669,24 +12674,24 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="279" hidden="false" outlineLevel="2">
+    <row r="279" hidden="true" outlineLevel="2">
       <c r="A279" t="s" s="35">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B279" t="s" s="5">
         <v>79</v>
       </c>
       <c r="C279" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D279" t="s" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E279" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F279" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G279" t="n" s="31">
         <v>46192.0</v>
@@ -12710,24 +12715,24 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="280" hidden="false" outlineLevel="2">
+    <row r="280" hidden="true" outlineLevel="2">
       <c r="A280" t="s" s="35">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B280" t="s" s="5">
         <v>79</v>
       </c>
       <c r="C280" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D280" t="s" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E280" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F280" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G280" t="n" s="31">
         <v>46192.0</v>
@@ -12751,24 +12756,24 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="281" hidden="false" outlineLevel="2">
+    <row r="281" hidden="true" outlineLevel="2">
       <c r="A281" t="s" s="35">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B281" t="s" s="5">
         <v>79</v>
       </c>
       <c r="C281" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D281" t="s" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E281" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F281" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G281" t="n" s="31">
         <v>46192.0</v>
@@ -12792,24 +12797,24 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="282" hidden="false" outlineLevel="2">
+    <row r="282" hidden="true" outlineLevel="2">
       <c r="A282" t="s" s="35">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B282" t="s" s="5">
         <v>79</v>
       </c>
       <c r="C282" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D282" t="s" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E282" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F282" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G282" t="n" s="31">
         <v>46192.0</v>
@@ -12833,24 +12838,24 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="283" hidden="false" outlineLevel="2">
+    <row r="283" hidden="true" outlineLevel="2">
       <c r="A283" t="s" s="35">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B283" t="s" s="5">
         <v>79</v>
       </c>
       <c r="C283" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D283" t="s" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E283" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F283" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G283" t="n" s="31">
         <v>46192.0</v>
@@ -12874,7 +12879,7 @@
         <v>46300.0</v>
       </c>
     </row>
-    <row r="284" hidden="false" outlineLevel="1">
+    <row r="284" hidden="true" outlineLevel="1">
       <c r="A284" t="s" s="23">
         <v>84</v>
       </c>
@@ -12901,24 +12906,24 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="285" hidden="false" outlineLevel="2">
+    <row r="285" hidden="true" outlineLevel="2">
       <c r="A285" t="s" s="35">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B285" t="s" s="5">
         <v>86</v>
       </c>
       <c r="C285" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D285" t="s" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E285" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F285" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G285" t="n" s="41">
         <v>46206.0</v>
@@ -12942,24 +12947,24 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="286" hidden="false" outlineLevel="2">
+    <row r="286" hidden="true" outlineLevel="2">
       <c r="A286" t="s" s="35">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B286" t="s" s="5">
         <v>86</v>
       </c>
       <c r="C286" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D286" t="s" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E286" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F286" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G286" t="n" s="41">
         <v>46206.0</v>
@@ -12983,24 +12988,24 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="287" hidden="false" outlineLevel="2">
+    <row r="287" hidden="true" outlineLevel="2">
       <c r="A287" t="s" s="35">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B287" t="s" s="5">
         <v>86</v>
       </c>
       <c r="C287" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D287" t="s" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E287" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F287" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G287" t="n" s="41">
         <v>46206.0</v>
@@ -13024,24 +13029,24 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="288" hidden="false" outlineLevel="2">
+    <row r="288" hidden="true" outlineLevel="2">
       <c r="A288" t="s" s="35">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B288" t="s" s="5">
         <v>86</v>
       </c>
       <c r="C288" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D288" t="s" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E288" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F288" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G288" t="n" s="41">
         <v>46206.0</v>
@@ -13065,24 +13070,24 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="289" hidden="false" outlineLevel="2">
+    <row r="289" hidden="true" outlineLevel="2">
       <c r="A289" t="s" s="35">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B289" t="s" s="5">
         <v>86</v>
       </c>
       <c r="C289" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D289" t="s" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E289" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F289" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G289" t="n" s="41">
         <v>46206.0</v>
@@ -13106,7 +13111,7 @@
         <v>46328.0</v>
       </c>
     </row>
-    <row r="290" hidden="false" outlineLevel="1">
+    <row r="290" hidden="true" outlineLevel="1">
       <c r="A290" t="s" s="23">
         <v>89</v>
       </c>
@@ -13133,24 +13138,24 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="291" hidden="false" outlineLevel="2">
+    <row r="291" hidden="true" outlineLevel="2">
       <c r="A291" t="s" s="35">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B291" t="s" s="5">
         <v>91</v>
       </c>
       <c r="C291" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D291" t="s" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E291" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F291" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G291" t="n" s="31">
         <v>46220.0</v>
@@ -13174,24 +13179,24 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="292" hidden="false" outlineLevel="2">
+    <row r="292" hidden="true" outlineLevel="2">
       <c r="A292" t="s" s="35">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B292" t="s" s="5">
         <v>91</v>
       </c>
       <c r="C292" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D292" t="s" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E292" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F292" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G292" t="n" s="31">
         <v>46220.0</v>
@@ -13215,24 +13220,24 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="293" hidden="false" outlineLevel="2">
+    <row r="293" hidden="true" outlineLevel="2">
       <c r="A293" t="s" s="35">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B293" t="s" s="5">
         <v>91</v>
       </c>
       <c r="C293" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D293" t="s" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E293" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F293" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G293" t="n" s="31">
         <v>46220.0</v>
@@ -13256,24 +13261,24 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="294" hidden="false" outlineLevel="2">
+    <row r="294" hidden="true" outlineLevel="2">
       <c r="A294" t="s" s="35">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B294" t="s" s="5">
         <v>91</v>
       </c>
       <c r="C294" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D294" t="s" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E294" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F294" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G294" t="n" s="31">
         <v>46220.0</v>
@@ -13297,24 +13302,24 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="295" hidden="false" outlineLevel="2">
+    <row r="295" hidden="true" outlineLevel="2">
       <c r="A295" t="s" s="35">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B295" t="s" s="5">
         <v>91</v>
       </c>
       <c r="C295" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D295" t="s" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E295" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F295" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G295" t="n" s="31">
         <v>46220.0</v>
@@ -13338,7 +13343,7 @@
         <v>46356.0</v>
       </c>
     </row>
-    <row r="296" hidden="false" outlineLevel="1">
+    <row r="296" hidden="true" outlineLevel="1">
       <c r="A296" t="s" s="23">
         <v>96</v>
       </c>
@@ -13365,24 +13370,24 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="297" hidden="false" outlineLevel="2">
+    <row r="297" hidden="true" outlineLevel="2">
       <c r="A297" t="s" s="35">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B297" t="s" s="5">
         <v>98</v>
       </c>
       <c r="C297" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D297" t="s" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E297" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F297" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G297" t="n" s="41">
         <v>46234.0</v>
@@ -13406,24 +13411,24 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="298" hidden="false" outlineLevel="2">
+    <row r="298" hidden="true" outlineLevel="2">
       <c r="A298" t="s" s="35">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B298" t="s" s="5">
         <v>98</v>
       </c>
       <c r="C298" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D298" t="s" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E298" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F298" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G298" t="n" s="41">
         <v>46234.0</v>
@@ -13447,24 +13452,24 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="299" hidden="false" outlineLevel="2">
+    <row r="299" hidden="true" outlineLevel="2">
       <c r="A299" t="s" s="35">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B299" t="s" s="5">
         <v>98</v>
       </c>
       <c r="C299" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D299" t="s" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E299" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F299" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G299" t="n" s="41">
         <v>46234.0</v>
@@ -13488,24 +13493,24 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="300" hidden="false" outlineLevel="2">
+    <row r="300" hidden="true" outlineLevel="2">
       <c r="A300" t="s" s="35">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B300" t="s" s="5">
         <v>98</v>
       </c>
       <c r="C300" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D300" t="s" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E300" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F300" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G300" t="n" s="41">
         <v>46234.0</v>
@@ -13529,24 +13534,24 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="301" hidden="false" outlineLevel="2">
+    <row r="301" hidden="true" outlineLevel="2">
       <c r="A301" t="s" s="35">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B301" t="s" s="5">
         <v>98</v>
       </c>
       <c r="C301" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D301" t="s" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E301" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F301" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G301" t="n" s="41">
         <v>46234.0</v>
@@ -13570,7 +13575,7 @@
         <v>46384.0</v>
       </c>
     </row>
-    <row r="302" hidden="false" outlineLevel="1">
+    <row r="302" hidden="true" outlineLevel="1">
       <c r="A302" t="s" s="23">
         <v>103</v>
       </c>
@@ -13597,24 +13602,24 @@
         <v>46412.0</v>
       </c>
     </row>
-    <row r="303" hidden="false" outlineLevel="2">
+    <row r="303" hidden="true" outlineLevel="2">
       <c r="A303" t="s" s="35">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B303" t="s" s="5">
         <v>105</v>
       </c>
       <c r="C303" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D303" t="s" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E303" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F303" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G303" t="n" s="31">
         <v>46248.0</v>
@@ -13638,24 +13643,24 @@
         <v>46412.0</v>
       </c>
     </row>
-    <row r="304" hidden="false" outlineLevel="2">
+    <row r="304" hidden="true" outlineLevel="2">
       <c r="A304" t="s" s="35">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B304" t="s" s="5">
         <v>105</v>
       </c>
       <c r="C304" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D304" t="s" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E304" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F304" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G304" t="n" s="31">
         <v>46248.0</v>
@@ -13679,24 +13684,24 @@
         <v>46412.0</v>
       </c>
     </row>
-    <row r="305" hidden="false" outlineLevel="2">
+    <row r="305" hidden="true" outlineLevel="2">
       <c r="A305" t="s" s="35">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B305" t="s" s="5">
         <v>105</v>
       </c>
       <c r="C305" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D305" t="s" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E305" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F305" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G305" t="n" s="31">
         <v>46248.0</v>
@@ -13720,24 +13725,24 @@
         <v>46412.0</v>
       </c>
     </row>
-    <row r="306" hidden="false" outlineLevel="2">
+    <row r="306" hidden="true" outlineLevel="2">
       <c r="A306" t="s" s="35">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B306" t="s" s="5">
         <v>105</v>
       </c>
       <c r="C306" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D306" t="s" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E306" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F306" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G306" t="n" s="31">
         <v>46248.0</v>
@@ -13761,24 +13766,24 @@
         <v>46412.0</v>
       </c>
     </row>
-    <row r="307" hidden="false" outlineLevel="2">
+    <row r="307" hidden="true" outlineLevel="2">
       <c r="A307" t="s" s="35">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B307" t="s" s="5">
         <v>105</v>
       </c>
       <c r="C307" t="s" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D307" t="s" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E307" t="s" s="7">
         <v>114</v>
       </c>
       <c r="F307" t="s" s="9">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G307" t="n" s="31">
         <v>46248.0</v>
@@ -13823,7 +13828,7 @@
     </row>
     <row r="309" hidden="false">
       <c r="A309" t="s" s="79">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B309" s="81"/>
       <c r="C309" s="83"/>
@@ -13863,22 +13868,22 @@
     </row>
     <row r="311" hidden="true" outlineLevel="1">
       <c r="A311" t="s" s="21">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B311" t="s" s="5">
         <v>22</v>
       </c>
       <c r="C311" t="s" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D311" t="n" s="7">
         <v>2.1</v>
       </c>
       <c r="E311" t="s" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F311" t="s" s="9">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G311" t="n" s="41">
         <v>46027.0</v>
@@ -13894,7 +13899,7 @@
       <c r="L311" s="7"/>
       <c r="M311" s="7"/>
       <c r="N311" t="s" s="11">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O311" t="s" s="11">
         <v>20</v>
@@ -13906,22 +13911,22 @@
     </row>
     <row r="312" hidden="true" outlineLevel="1">
       <c r="A312" t="s" s="23">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B312" t="s" s="25">
         <v>37</v>
       </c>
       <c r="C312" t="s" s="27">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D312" t="n" s="27">
         <v>1.1</v>
       </c>
       <c r="E312" t="s" s="27">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F312" t="s" s="29">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G312" t="n" s="31">
         <v>46083.0</v>
@@ -13949,22 +13954,22 @@
     </row>
     <row r="313" hidden="true" outlineLevel="1">
       <c r="A313" t="s" s="21">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B313" t="s" s="5">
         <v>44</v>
       </c>
       <c r="C313" t="s" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D313" t="n" s="7">
         <v>2.2</v>
       </c>
       <c r="E313" t="s" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F313" t="s" s="9">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G313" t="n" s="41">
         <v>46111.0</v>
@@ -13992,22 +13997,22 @@
     </row>
     <row r="314" hidden="true" outlineLevel="1">
       <c r="A314" t="s" s="23">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B314" t="s" s="25">
         <v>51</v>
       </c>
       <c r="C314" t="s" s="27">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D314" t="n" s="27">
         <v>1.2</v>
       </c>
       <c r="E314" t="s" s="27">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F314" t="s" s="29">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G314" t="n" s="31">
         <v>46129.0</v>
@@ -14035,22 +14040,22 @@
     </row>
     <row r="315" hidden="true" outlineLevel="1">
       <c r="A315" t="s" s="21">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B315" t="s" s="5">
         <v>58</v>
       </c>
       <c r="C315" t="s" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D315" t="n" s="7">
         <v>2.3</v>
       </c>
       <c r="E315" t="s" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F315" t="s" s="9">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G315" t="n" s="41">
         <v>46143.0</v>
@@ -14078,22 +14083,22 @@
     </row>
     <row r="316" hidden="true" outlineLevel="1">
       <c r="A316" t="s" s="23">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B316" t="s" s="25">
         <v>65</v>
       </c>
       <c r="C316" t="s" s="27">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D316" t="n" s="27">
         <v>1.3</v>
       </c>
       <c r="E316" t="s" s="27">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F316" t="s" s="29">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G316" t="n" s="31">
         <v>46157.0</v>
@@ -14121,22 +14126,22 @@
     </row>
     <row r="317" hidden="true" outlineLevel="1">
       <c r="A317" t="s" s="21">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B317" t="s" s="5">
         <v>72</v>
       </c>
       <c r="C317" t="s" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D317" t="n" s="7">
         <v>2.4</v>
       </c>
       <c r="E317" t="s" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F317" t="s" s="9">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G317" t="n" s="41">
         <v>46175.0</v>
@@ -14164,22 +14169,22 @@
     </row>
     <row r="318" hidden="true" outlineLevel="1">
       <c r="A318" t="s" s="23">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B318" t="s" s="25">
         <v>79</v>
       </c>
       <c r="C318" t="s" s="27">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D318" t="n" s="27">
         <v>1.4</v>
       </c>
       <c r="E318" t="s" s="27">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F318" t="s" s="29">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G318" t="n" s="31">
         <v>46192.0</v>
@@ -14207,22 +14212,22 @@
     </row>
     <row r="319" hidden="true" outlineLevel="1">
       <c r="A319" t="s" s="21">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B319" t="s" s="5">
         <v>86</v>
       </c>
       <c r="C319" t="s" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D319" t="n" s="7">
         <v>2.5</v>
       </c>
       <c r="E319" t="s" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F319" t="s" s="9">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G319" t="n" s="41">
         <v>46206.0</v>
@@ -14250,22 +14255,22 @@
     </row>
     <row r="320" hidden="true" outlineLevel="1">
       <c r="A320" t="s" s="23">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B320" t="s" s="25">
         <v>91</v>
       </c>
       <c r="C320" t="s" s="27">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D320" t="n" s="27">
         <v>1.5</v>
       </c>
       <c r="E320" t="s" s="27">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F320" t="s" s="29">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G320" t="n" s="31">
         <v>46220.0</v>
@@ -14293,22 +14298,22 @@
     </row>
     <row r="321" hidden="true" outlineLevel="1">
       <c r="A321" t="s" s="21">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B321" t="s" s="5">
         <v>98</v>
       </c>
       <c r="C321" t="s" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D321" t="n" s="7">
         <v>2.6</v>
       </c>
       <c r="E321" t="s" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F321" t="s" s="9">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G321" t="n" s="41">
         <v>46234.0</v>
@@ -14336,22 +14341,22 @@
     </row>
     <row r="322" hidden="true" outlineLevel="1">
       <c r="A322" t="s" s="23">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B322" t="s" s="25">
         <v>105</v>
       </c>
       <c r="C322" t="s" s="27">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D322" t="n" s="27">
         <v>1.6</v>
       </c>
       <c r="E322" t="s" s="27">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F322" t="s" s="29">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G322" t="n" s="31">
         <v>46248.0</v>
@@ -14414,16 +14419,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2"/>
@@ -14443,7 +14448,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B1" t="n" s="86">
         <v>2.0</v>
@@ -14451,7 +14456,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B2" t="n" s="86">
         <v>0.0</v>
@@ -14459,7 +14464,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B3" t="n" s="87">
         <v>90.08</v>
@@ -14467,7 +14472,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B4" t="n" s="86">
         <v>14.0</v>
@@ -14475,7 +14480,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B5" t="n" s="86">
         <v>6.0</v>
@@ -14483,7 +14488,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B6" t="n" s="86">
         <v>53.0</v>
@@ -14491,7 +14496,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B7" t="n" s="86">
         <v>59.0</v>
@@ -14499,7 +14504,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B8" t="n" s="86">
         <v>80.0</v>
@@ -14507,7 +14512,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B9" t="n" s="86">
         <v>102.0</v>
@@ -14515,7 +14520,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B10" t="n" s="86">
         <v>97.0</v>
@@ -14523,7 +14528,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B11" t="n" s="86">
         <v>108.0</v>
@@ -14531,7 +14536,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B12" t="n" s="86">
         <v>122.0</v>
@@ -14539,7 +14544,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B13" t="n" s="86">
         <v>136.0</v>
@@ -14547,7 +14552,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B14" t="n" s="86">
         <v>150.0</v>
@@ -14555,7 +14560,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B15" t="n" s="86">
         <v>164.0</v>
@@ -14563,7 +14568,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B16" t="n" s="86">
         <v>0.0</v>
@@ -14571,7 +14576,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B17" t="n" s="86">
         <v>0.0</v>
@@ -14579,7 +14584,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B18" t="n" s="86">
         <v>0.0</v>
@@ -14587,7 +14592,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B19" t="n" s="86">
         <v>0.0</v>
@@ -14595,7 +14600,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B20" t="n" s="86">
         <v>0.0</v>
@@ -14603,7 +14608,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B21" t="n" s="86">
         <v>0.0</v>
@@ -14611,7 +14616,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B22" t="n" s="86">
         <v>0.0</v>
@@ -14619,7 +14624,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B23" t="n" s="86">
         <v>0.0</v>
@@ -14627,7 +14632,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B24" t="n" s="86">
         <v>0.0</v>
@@ -14635,7 +14640,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B25" t="n" s="86">
         <v>0.0</v>
@@ -14643,7 +14648,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B26" t="n" s="86">
         <v>0.0</v>
@@ -14651,7 +14656,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B27" t="n" s="86">
         <v>0.0</v>
@@ -14659,7 +14664,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B28" t="n" s="86">
         <v>0.0</v>
@@ -14667,7 +14672,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B29" t="n" s="86">
         <v>0.0</v>
@@ -14675,7 +14680,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B30" t="n" s="86">
         <v>0.0</v>
@@ -14683,7 +14688,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B31" t="n" s="86">
         <v>0.0</v>
@@ -14691,7 +14696,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B32" t="n" s="86">
         <v>0.0</v>
@@ -14699,7 +14704,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B33" t="n" s="86">
         <v>0.0</v>
@@ -14707,7 +14712,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B34" t="n" s="86">
         <v>0.0</v>
@@ -14715,7 +14720,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B35" t="n" s="86">
         <v>0.0</v>
@@ -14723,7 +14728,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B36" t="n" s="86">
         <v>0.0</v>
@@ -14731,7 +14736,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B37" t="n" s="86">
         <v>0.0</v>
@@ -14739,7 +14744,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B38" t="n" s="86">
         <v>0.0</v>
@@ -14747,7 +14752,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B39" t="n" s="86">
         <v>0.0</v>
@@ -14755,7 +14760,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B40" t="n" s="86">
         <v>68.0</v>
@@ -14763,7 +14768,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B41" t="n" s="86">
         <v>-39.0</v>
@@ -14771,7 +14776,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B42" t="n" s="86">
         <v>94.0</v>
@@ -14779,7 +14784,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B43" t="n" s="86">
         <v>122.0</v>
@@ -14787,7 +14792,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B44" t="n" s="86">
         <v>136.0</v>
@@ -14795,7 +14800,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B45" t="n" s="86">
         <v>164.0</v>
@@ -14803,7 +14808,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B46" t="n" s="86">
         <v>178.0</v>
@@ -14811,7 +14816,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B47" t="n" s="86">
         <v>21.0</v>
@@ -14819,7 +14824,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B48" t="n" s="86">
         <v>49.0</v>
@@ -14827,7 +14832,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B49" t="n" s="86">
         <v>77.0</v>
@@ -14835,7 +14840,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B50" t="n" s="86">
         <v>75.0</v>
@@ -14843,7 +14848,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B51" t="n" s="86">
         <v>103.0</v>
@@ -14851,7 +14856,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B52" t="n" s="86">
         <v>131.0</v>
@@ -14859,7 +14864,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B53" t="n" s="86">
         <v>-14.0</v>
@@ -14867,7 +14872,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B54" t="n" s="86">
         <v>49.0</v>
@@ -14875,7 +14880,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B55" t="n" s="86">
         <v>63.0</v>
@@ -14883,7 +14888,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B56" t="n" s="86">
         <v>77.0</v>
@@ -14891,7 +14896,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B57" t="n" s="86">
         <v>91.0</v>
@@ -14899,7 +14904,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B58" t="n" s="86">
         <v>105.0</v>
@@ -14907,7 +14912,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B59" t="n" s="86">
         <v>119.0</v>
@@ -14915,7 +14920,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B60" t="n" s="86">
         <v>133.0</v>
@@ -14923,7 +14928,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B61" t="n" s="86">
         <v>147.0</v>
@@ -14931,7 +14936,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B62" t="n" s="86">
         <v>161.0</v>
@@ -14939,7 +14944,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B63" t="n" s="86">
         <v>175.0</v>
@@ -14947,7 +14952,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B64" t="n" s="86">
         <v>189.0</v>
@@ -14955,7 +14960,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B65" t="n" s="86">
         <v>0.0</v>
@@ -14963,7 +14968,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B66" t="n" s="86">
         <v>0.0</v>
@@ -14971,7 +14976,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B67" t="n" s="86">
         <v>0.0</v>
@@ -14979,7 +14984,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B68" t="n" s="86">
         <v>0.0</v>
@@ -14987,7 +14992,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B69" t="n" s="86">
         <v>0.0</v>
@@ -14995,7 +15000,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B70" t="n" s="86">
         <v>0.0</v>
@@ -15003,7 +15008,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B71" t="n" s="86">
         <v>0.0</v>
@@ -15011,7 +15016,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B72" t="n" s="86">
         <v>0.0</v>
@@ -15019,7 +15024,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B73" t="n" s="86">
         <v>0.0</v>
@@ -15027,7 +15032,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B74" t="n" s="86">
         <v>0.0</v>
@@ -15035,7 +15040,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B75" t="n" s="86">
         <v>0.0</v>
@@ -15043,7 +15048,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B76" t="n" s="86">
         <v>0.0</v>
@@ -15051,7 +15056,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B77" t="n" s="86">
         <v>86.0</v>
@@ -15059,7 +15064,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B78" t="n" s="86">
         <v>149.0</v>
@@ -15067,7 +15072,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B79" t="n" s="86">
         <v>170.0</v>
@@ -15075,7 +15080,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B80" t="n" s="86">
         <v>191.0</v>
@@ -15083,7 +15088,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B81" t="n" s="86">
         <v>156.0</v>
@@ -15091,7 +15096,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B82" t="n" s="86">
         <v>177.0</v>
@@ -15099,7 +15104,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B83" t="n" s="86">
         <v>170.0</v>
@@ -15107,7 +15112,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B84" t="n" s="86">
         <v>191.0</v>
@@ -15115,7 +15120,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B85" t="n" s="86">
         <v>191.0</v>
@@ -15123,7 +15128,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B86" t="n" s="86">
         <v>212.0</v>
@@ -15131,7 +15136,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B87" t="n" s="86">
         <v>184.0</v>
@@ -15139,7 +15144,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B88" t="n" s="86">
         <v>205.0</v>
@@ -15147,7 +15152,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B89" t="n" s="86">
         <v>34.0</v>
@@ -15155,7 +15160,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B90" t="n" s="86">
         <v>96.0</v>
@@ -15163,7 +15168,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B91" t="n" s="86">
         <v>104.0</v>
@@ -15171,7 +15176,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B92" t="n" s="86">
         <v>109.0</v>
@@ -15179,7 +15184,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B93" t="n" s="86">
         <v>96.0</v>
@@ -15187,7 +15192,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B94" t="n" s="86">
         <v>103.0</v>
@@ -15195,7 +15200,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B95" t="n" s="86">
         <v>111.0</v>
@@ -15203,7 +15208,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B96" t="n" s="86">
         <v>125.0</v>
@@ -15211,7 +15216,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B97" t="n" s="86">
         <v>133.0</v>
@@ -15219,7 +15224,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B98" t="n" s="86">
         <v>150.0</v>
@@ -15227,7 +15232,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B99" t="n" s="86">
         <v>164.0</v>
@@ -15235,7 +15240,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B100" t="n" s="86">
         <v>178.0</v>
@@ -15243,7 +15248,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B101" t="n" s="86">
         <v>0.0</v>
@@ -15251,7 +15256,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B102" t="n" s="86">
         <v>0.0</v>
@@ -15259,7 +15264,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B103" t="n" s="86">
         <v>0.0</v>
@@ -15267,7 +15272,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B104" t="n" s="86">
         <v>0.0</v>
@@ -15275,7 +15280,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B105" t="n" s="86">
         <v>0.0</v>
@@ -15283,7 +15288,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B106" t="n" s="86">
         <v>0.0</v>
@@ -15291,7 +15296,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B107" t="n" s="86">
         <v>0.0</v>
@@ -15299,7 +15304,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B108" t="n" s="86">
         <v>0.0</v>
@@ -15307,7 +15312,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B109" t="n" s="86">
         <v>0.0</v>
@@ -15315,7 +15320,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B110" t="n" s="86">
         <v>0.0</v>
@@ -15323,7 +15328,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B111" t="n" s="86">
         <v>0.0</v>
@@ -15331,7 +15336,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B112" t="n" s="86">
         <v>0.0</v>
@@ -15339,7 +15344,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B113" t="n" s="86">
         <v>0.0</v>
@@ -15347,7 +15352,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B114" t="n" s="86">
         <v>0.0</v>
@@ -15355,7 +15360,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B115" t="n" s="86">
         <v>0.0</v>
@@ -15363,7 +15368,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B116" t="n" s="86">
         <v>0.0</v>
@@ -15371,7 +15376,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B117" t="n" s="86">
         <v>0.0</v>
@@ -15379,7 +15384,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B118" t="n" s="86">
         <v>0.0</v>
@@ -15387,7 +15392,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B119" t="n" s="86">
         <v>0.0</v>
@@ -15395,7 +15400,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B120" t="n" s="86">
         <v>0.0</v>
@@ -15403,7 +15408,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B121" t="n" s="86">
         <v>0.0</v>
@@ -15411,7 +15416,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B122" t="n" s="86">
         <v>0.0</v>
@@ -15419,7 +15424,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B123" t="n" s="86">
         <v>0.0</v>
@@ -15427,7 +15432,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B124" t="n" s="86">
         <v>0.0</v>
@@ -15435,7 +15440,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B125" t="n" s="86">
         <v>49.0</v>
@@ -15443,7 +15448,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B126" t="n" s="86">
         <v>77.0</v>
@@ -15451,7 +15456,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B127" t="n" s="86">
         <v>105.0</v>
@@ -15459,7 +15464,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B128" t="n" s="86">
         <v>118.0</v>
@@ -15467,7 +15472,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B129" t="n" s="86">
         <v>131.0</v>
@@ -15475,7 +15480,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B130" t="n" s="86">
         <v>146.0</v>
@@ -15483,7 +15488,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B131" t="n" s="86">
         <v>157.0</v>
@@ -15491,7 +15496,7 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B132" t="n" s="86">
         <v>167.0</v>
@@ -15499,7 +15504,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B133" t="n" s="86">
         <v>180.0</v>
@@ -15507,7 +15512,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B134" t="n" s="86">
         <v>195.0</v>
@@ -15515,7 +15520,7 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B135" t="n" s="86">
         <v>209.0</v>
@@ -15523,7 +15528,7 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B136" t="n" s="86">
         <v>223.0</v>
